--- a/public/한국영화top500.xlsx
+++ b/public/한국영화top500.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ehdgn\Desktop\superIP\superip\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B12BBD9B-B62A-41DB-A7F7-903D6BDD84FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6116C5-5CDD-4DCC-B44F-040433D3BADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16140" yWindow="2295" windowWidth="16200" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3553" uniqueCount="2045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3946" uniqueCount="2437">
   <si>
     <t>id</t>
   </si>
@@ -6158,6 +6158,1295 @@
   </si>
   <si>
     <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20200706_191%2F1594001490577tifkl_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_32%2F1324577751718PR2XX_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20191113_203%2F1573610067050zNCj1_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_297%2F13245808608977LUGh_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20121113_61%2F1352790997902R2e2S_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_77%2F1324579716549Q2mSQ_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_71%2F1324560524659M2GQd_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20180103_83%2F1514944124667mI6T8_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20120220_121%2F13297199672554wCnW_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20120821_15%2F1345527791595gJNze_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_154%2F1324559577487KR6mo_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20170206_116%2F1486347780659NI0zd_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20200122_181%2F15796574636309Fux2_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190128_284%2F1548637887932Dwfkj_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20130902_77%2F1378097897693bPzFw_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_142%2F1324646482436YSvXF_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_17%2F13246445819513a0iD_GIF%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_5%2F1324641135319CFXC5_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_296%2F1324558713277YVGi7_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_262%2F132455007716617FoB_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_252%2F13245453708584yy8Q_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_19%2F1324565742630Mfmdk_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_163%2F1324580679545RJvej_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_99%2F1324630120059FA5J4_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_228%2F13246018575638l5Bv_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_213%2F1324612062528fkaOi_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_143%2F13245581455966vv77_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_99%2F1324528238530pQD3L_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_60%2F1324563260023fIg8W_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_129%2F1324578619064nHMBx_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_82%2F1324641257061OKJu8_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_205%2F132457019000969gj4_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20211122_91%2F1637564743461raGXe_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_83%2F1324563888923UaJGN_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_113%2F1324639306448L7EXF_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_16%2F1324586596408pX3QO_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_211%2F1324564095902Gm54X_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20210726_114%2F1627265960693kkM0B_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20150423_156%2F1429750778654FEw2V_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_74%2F1324560950013hmyqS_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_16%2F1324556838975kfK1M_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_205%2F1324629742378RJsDQ_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20231004_194%2F1696419602810jWf6f_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_179%2F1324626012857BRHBe_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_124%2F1324590015319ihgR4_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20140603_16%2F1401760272322q7OHX_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111224_109%2F13246554789677iLlv_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20140915_276%2F1410743528390C7H2D_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_277%2F1324552513048rsEN9_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20161021_136%2F1477013820750RNsJu_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20120127_206%2F1327645723391luuVn_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20160519_248%2F1463650220674Q7dRl_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_219%2F1324537979383HEXHt_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20130429_285%2F1367199572646THiIp_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_81%2F1324568746389gSERh_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20180920_268%2F1537425274130wtXzB_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20151021_172%2F14453964781624mCqX_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_272%2F1324627884224BolLz_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_199%2F1324585121142uJCi3_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_223%2F1324569385664b0OV6_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20220718_224%2F1658121739465fgRof_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20150820_140%2F14400325489289j4Fh_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20160616_172%2F1466040138501VYf7a_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_42%2F1324547822243la2mY_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_163%2F1324569921967OfPqh_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20191231_207%2F1577754153157vUcFn_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_288%2F1324561365013I9PW5_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20220824_252%2F1661324514413czYBf_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20140107_123%2F1389085171684kz15g_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_266%2F1324558463907JwOy7_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20180828_55%2F15354321217227X7a3_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_132%2F1324565989317NuXLH_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_178%2F1324590437150gH76T_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20181204_172%2F1543891228332kV3d1_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20230927_209%2F16957874505258ntm3_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_9%2F13245274330709gy4C_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_4%2F13245690836748vDcS_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20220607_129%2F16545872892918GA4h_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20150116_12%2F1421375158277WwbIK_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_279%2F13246305442071SlF5_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_33%2F13245504982319tN93_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_193%2F13246223871889i3vD_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20120515_187%2F1337071991340NIfrE_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_62%2F1324631973056f30UA_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20130305_119%2F1362462163364VI5fv_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20181126_96%2F1543207321602QPWG8_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_289%2F1324571961521EJaTM_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_206%2F1324584875309SbXGe_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20170517_278%2F1494985832213VQ7uH_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20131206_283%2F1386292376595PICSR_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_41%2F1324620268521WGqqX_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_20%2F1324528755469Ipibv_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20121114_241%2F13528614978854Dzjy_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190115_40%2F15475402622236yHgr_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_282%2F1324574854291prB4X_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190821_179%2F1566364206702zsxW4_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_149%2F1324590430199VL2Cw_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_209%2F1324506098766WXErd_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20200703_48%2F1593739617223iuD2b_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_136%2F1324584593657In7jl_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_133%2F1324540820808UuBE3_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20131023_158%2F1382497408356OByMJ_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20151127_238%2F1448605940320G8pwH_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20140826_174%2F1409016626929bOFP8_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_265%2F1324571164029SsBha_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_16%2F1324556860093kJnSp_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20130313_237%2F1363139448527fNW0l_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_46%2F1324527877699IiMOa_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20210210_269%2F1612936327829TMifx_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_44%2F1324495279035H3vpT_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20120109_223%2F1326074891823WB4wS_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20221227_112%2F16721270739480lDiS_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20200929_240%2F1601370752754trKxu_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_159%2F1324631319677HxdWv_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20130228_105%2F1362026575599uE2wA_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20150128_263%2F1422410206018A2rmx_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20240124_126%2F1706084548964mScff_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_184%2F13245730000367KK9o_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common/?src=http%3A%2F%2Fblogfiles.naver.net%2FMjAyMzA0MjNfMjYw%2FMDAxNjgyMTgzMzgyOTU4.FG452VEiSLJS-QkMrGnnFeNXah65rztDrzDGKJS5CpUg.OR8sR39todZl_FubRFJ65k6yK5J8oRY-rFcM4F5-5bgg.PNG.snow8845%2F1.png&amp;type=sc960_832</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_232%2F1324561869593LVuBY_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_166%2F1324591011429sMMDJ_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_224%2F1324566944253ErNPq_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20140113_7%2F1389586752116DnTAF_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20181205_284%2F1543974277191S4IrC_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20120824_74%2F1345791296899zasNv_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_56%2F13246314342663riGK_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20210923_298%2F1632376015399DWJAd_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20170426_111%2F14931684846956pCQV_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190418_272%2F155557683107045leS_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20140902_26%2F1409617728644vaaT6_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_272%2F13245594485196UiVf_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20140219_282%2F1392770316591Jvcos_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_275%2F1324568615891ca15N_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20120127_155%2F1327639091393mM8op_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_30%2F1324560316848SBA2J_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190625_168%2F1561426986010A3uBi_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_153%2F1324517212070OhruJ_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20230921_142%2F1695281375835uM9nx_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20181001_87%2F15383614506431bq1D_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20151022_238%2F14454965912030NtfT_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_112%2F1324538077177Sg9W4_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190805_26%2F1564994340344jQru8_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common/?src=http%3A%2F%2Fblogfiles.naver.net%2F20130610_86%2Fa5827199_137083092955769msP_JPEG%2F%25BF%25CD%25C0%25CF%25B5%25E5_%25C4%25AB%25B5%25E52.jpg.jpg&amp;type=ff332_332</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20201021_273%2F16032618054109Yvje_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_4%2F1324622952437bs3AI_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_209%2F13245610161742LqXE_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_30%2F1324556614845pqDku_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20181109_210%2F1541739608888DcEEo_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_171%2F1324557016667yl6r3_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20201104_45%2F160445535053439akc_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_233%2F1324486884038nu8Xk_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20220824_35%2F1661308127186TYDre_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_75%2F1324572603254Y8Dqn_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_102%2F1324585715572s9HYe_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_14%2F1324579666463jz4Fs_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_227%2F1324577767463k3m94_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111224_242%2F1324655769176S2HlM_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20180130_167%2F1517289346533DfzLE_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_99%2F1324563099360p8owb_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111221_287%2F1324459869081HLqed_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_35%2F1324535472152cA18c_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190404_182%2F1554340290133Khnb5_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20140714_232%2F1405299488288uux6D_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20150421_177%2F1429594492778jo5JN_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20230906_145%2F1693965381891wjuK6_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_93%2F1324558587016BnNf9_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_49%2F1324562848431OtabS_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20140513_153%2F1399943714031tPTCC_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_245%2F1324557741051pUg2k_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20160512_132%2F1463043558461I0pL1_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20231215_228%2F1702622558194p8LNL_PNG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20210831_152%2F1630371935224qy9s6_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_139%2F1324611426860egoAM_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_293%2F13245607203545xfG9_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20230816_203%2F1692186449098K0QIb_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20171129_172%2F1511930306592dumMz_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20180129_75%2F1517203407129cCrpT_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_159%2F1324559177246WhKy4_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20170818_225%2F1503022966358iQcyu_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_44%2F1324559146453T68Tb_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20170419_128%2F1492582031650Pk5Iq_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20120525_154%2F1337928978163FdVHo_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20120330_232%2F13330707720243Ohcq_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20180209_36%2F1518146280303ogba8_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20220126_99%2F16431781439406dpnP_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20130621_233%2F1371797615455UpX9U_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_236%2F1324594334991pa92c_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20180219_109%2F15190203631845L35p_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_200%2F1324565396985m4uz5_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20120917_299%2F13478715604590BRRM_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_279%2F1324573017175xJisQ_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20170717_299%2F1500255989773woYLE_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20210810_123%2F16285742137853XFs3_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_124%2F1324505338121K8dq1_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_190%2F1324537910062a2DUo_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_299%2F1324587041674vE43S_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_284%2F1324567034133MLvie_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_180%2F1324553225881GvQnX_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_139%2F1324581156922AnCdY_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_68%2F1324566680122MUuwc_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_248%2F1324586136879y2UyS_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20220511_189%2F1652251073330PXNoG_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common/?src=http%3A%2F%2Fblogfiles.naver.net%2FMjAyNDAyMDNfMjYw%2FMDAxNzA2ODkwMjM2MTg1.A1eRhOi4ZoGXCQFS4YaeyB4J3DqguoK1330C4m-hs1wg.xSeAuh4CZvYTdZaaHPoN871cHYD6htWKGa6yW_6_6N4g.JPEG.ecstrance%2F5fmGsitJDQDF5NIU9ksa0iCpNOT.jpg&amp;type=sc960_832</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20120319_260%2F1332141512506f2o7n_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190806_57%2F1565060277522KjSpd_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_262%2F1324563538445QUOvS_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20160616_68%2F1466039997062rJ2kf_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190918_70%2F1568789034699xL82H_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_37%2F1324559410756qeD33_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_156%2F1324580751019QgaE8_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20240516_147%2F1715830347927Txj0U_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_28%2F1324583595326mcRef_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20200812_245%2F159719521887011fjF_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_135%2F1324623801598CY7zg_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common/?src=http%3A%2F%2Fblogfiles.naver.net%2FMjAyMzA0MjlfNjYg%2FMDAxNjgyNzQ5MTMzODk3.lTyFlu8QxRzkZtxGqXwi0TesMiXHHBRuIEtSyuXm_AIg.VKyop4pBcrH7CRQOvCP28kJ0UtZGoF5y296alvLPN-wg.PNG.snow8845%2F1.png&amp;type=sc960_832</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20200115_223%2F1579061805057fDTGd_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20140124_268%2F1390525769948zPLtK_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20131021_235%2F1382319595546Kih6p_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20130912_182%2F1378966757505CMozp_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20170510_67%2F1494379581052e3Eqd_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_119%2F1324572033280cHnKk_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_176%2F1324536930481yx2Tb_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_288%2F1324570657352qy8Uq_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20160317_297%2F1458178138484vOfhJ_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20120717_85%2F1342520125886dDFBX_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20130527_14%2F1369619178466YJEdA_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190329_223%2F1553847778414CTAcF_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_272%2F13245600475602dnco_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20180316_177%2F1521164667488clVxP_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_220%2F1324557470213qkBOP_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_225%2F1324535496569Ftrri_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190828_246%2F1566958975223z5NAU_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20141124_290%2F1416806846614dwfvP_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_36%2F1324558778398r77Tm_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20240206_234%2F1707210318193MxCbW_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20220929_135%2F1664441921246ae2RC_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20141007_203%2F1412647184329k1jAF_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20160205_299%2F1454651273096sYmsK_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20161124_88%2F1479951959050RqcvW_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20200910_230%2F1599726950402rAsY6_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20150318_228%2F1426655040206Cddhq_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_157%2F1324519943849vNdR3_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_188%2F1324496857786HVEmy_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20121207_178%2F1354844520791svGqw_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190207_119%2F1549515732449nv5tM_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20161130_126%2F1480469003419ruzKF_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_107%2F1324599151677AKNgW_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_298%2F1324572110503Mhros_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20130429_248%2F1367215419295wENEK_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190821_138%2F1566362458427V6Usp_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_132%2F1324628107015N7LC5_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20170515_244%2F1494811036725cqdRH_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common/?src=http%3A%2F%2Fimgnews.naver.net%2Fimage%2F5291%2F2022%2F11%2F13%2F0001668094_001_20221113221801714.jpg&amp;type=sc960_832</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20151008_292%2F1444285146770iilaH_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20230403_204%2F1680507641170NKvOl_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_66%2F1324573637310vK53G_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_159%2F1324545752818TXrvb_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_134%2F1324651725315JHbrY_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20120925_204%2F1348562559451uq2du_JPEG%2Fmovie_image.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20150430_251%2F1430368834167yWRPA_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20150608_24%2F1433748911488tSrPE_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_299%2F1324607700505DS7MK_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20190603_86%2F15595468699485F3e6_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20240705_147%2F1720142916385Hwze0_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_194%2F1324562662652y5cSJ_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_292%2F1324499627233nVOsh_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20160121_19%2F1453360481455FIfHz_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_198%2F1324557105768JuTCe_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20160229_206%2F1456706753369JeRAH_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_290%2F1324635470354Nny0f_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20230802_198%2F1690967873095A7TxE_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111222_130%2F1324537003406fndmH_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20131010_6%2F13813691620905t8o2_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20151007_38%2F1444181759217Hq61u_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?quality=75&amp;direct=true&amp;src=https%3A%2F%2Fmovie-phinf.pstatic.net%2F20111223_240%2F1324619270798bO3Vy_JPEG%2Fmovie_image.jpg</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20220805_227%2F1659685387586PIORG_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_76%2F13245566966411zUwg_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20160523_204%2F14639851237601hEGQ_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20131126_243%2F13854340134117wiXM_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20120227_164%2F1330332687398PQ1U3_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_263%2F1324562989916mICvG_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_119%2F1324568569252gaHjb_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111221_132%2F1324473774319Tty3v_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20120111_126%2F1326265238733Y8yPb_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_44%2F1324567143749EUxfp_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20171107_251%2F1510033896133nWqxG_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20140819_243%2F1408432915315hGXts_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_45%2F1324548952997QWvqm_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20121204_164%2F1354603402996ixgxY_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_84%2F1324562591095UcFCp_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20150112_87%2F1421029065463Ajc9k_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20140404_158%2F13965930899877qfjc_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20230809_114%2F1691559109714F3JPy_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20171013_225%2F1507872096788TxEL5_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20200624_137%2F15929908359489lOON_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20180910_81%2F1536543365477xFgPy_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_245%2F1324573082537ukhk0_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20181105_232%2F1541392865465aVb5V_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_186%2F1324563337863OLb03_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20191024_215%2F1571900079078PNazL_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_268%2F1324566765333lxqHM_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20210820_122%2F1629448997924YXUCv_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20160120_81%2F1453251627428vz7d8_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20140603_16%2F1401760272322q7OHX_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_14%2F1324487802154g67pO_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_281%2F1324585025299Qk3u2_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20120117_128%2F1326792036128WSKQp_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20140424_211%2F1398315678038omnHU_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20180122_124%2F1516586697016QmvO1_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_92%2F1324617493049722lv_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20190306_280%2F1551849045570X4iac_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_44%2F1324618561837t2XF2_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20190515_203%2F1557888285764Rvouz_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20221123_65%2F1669168819647KdX9K_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20200117_56%2F1579237723353mX1fB_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20170908_108%2F1504837489518BdEBl_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20221213_158%2F1670910727328mpqYu_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20131114_260%2F1384391087931T5Yx8_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20180710_211%2F1531198746645nsdKN_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20180525_232%2F15272144254888eehd_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_201%2F1324563595362wx638_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_102%2F1324539323323xQi1t_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_21%2F1324536158982tdOto_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_107%2F1324567301859BEymJ_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_220%2F1324561708014ElEtU_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_233%2F1324639941468SWAle_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20130724_142%2F13746405224183NYOy_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_184%2F1324495774928y3gEe_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_232%2F1324532908022sVKFz_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_139%2F1324558403168ecS5n_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_190%2F13246006004520wFif_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_282%2F1324579813186mheJA_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_281%2F1324563437767d08oK_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20150224_107%2F1424739640757P3Xc6_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_62%2F1324525135338kzsOO_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_214%2F1324614479718DP8fd_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_73%2F1324580384197iEUoH_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111224_210%2F1324654218231hH5uy_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20131022_132%2F1382420527745tlEd3_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20121105_88%2F1352083721604Kzds7_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_229%2F1324561292259Popef_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_104%2F1324638521898Mtz5U_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20170308_197%2F1488935001510TfDtR_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20190911_29%2F1568167420523xeKY5_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_34%2F13246299046080kAgY_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111221_56%2F1324479001417vejzF_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20181227_80%2F1545901137289EGbWK_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20150515_16%2F1431653299268yvog1_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20140422_100%2F1398126186037Pyxnt_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20180730_82%2F15329286640280Wu1t_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20220615_63%2F1655270906406BGdFF_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_256%2F1324522564673XWf9p_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_235%2F1324625472367kWNBr_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_269%2F1324571435558EQ0PH_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_36%2F1324623625436gK7bm_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20121011_241%2F1349930904051M4Q8m_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20130902_68%2F1378096688321WUTwq_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_52%2F1324584126987ikzz5_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20180406_37%2F1522991036857QqP7N_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20171030_272%2F1509348877448FqDsF_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20120517_262%2F13372165737985RsHR_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20150824_144%2F14403775273784piJ0_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20180305_19%2F1520225513539qKxjR_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20150415_257%2F1429075626914yLhHW_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20160819_21%2F1471568371621ENt4D_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20170404_270%2F14912701138864TMXE_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_251%2F1324593350868ov2zn_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_181%2F13245700678482pB2N_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_205%2F1324527902150wyjno_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20141201_71%2F1417408474779DSEyl_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20190226_194%2F15511480897441tE6t_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_65%2F1324584807900CTMuA_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20180713_27%2F1531446268141JEyKE_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20170206_87%2F1486347556947SbfPd_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_125%2F13245831165239qaBB_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20181031_241%2F1540950975705Bac4v_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_49%2F1324559296530Ns2Xc_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20220928_85%2F1664332929020nYWPc_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_189%2F1324563309262eeOWt_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20181123_36%2F1542956277015JmOTd_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_212%2F1324558915334iXFAf_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20130308_253%2F1362719056056lPsEK_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111223_272%2F1324582230529ThbiW_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20170210_40%2F1486707180853wnm7T_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_289%2F1324557978896PYeBX_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_198%2F1324557143145FQSLd_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common/?src=http%3A%2F%2Fblogfiles.naver.net%2F20091013_125%2Fxellosoo_1255412150882c0lOF_jpg%2Fserect_teaser_poster_xellosoo.jpg&amp;type=sc960_832</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common/?src=http%3A%2F%2Fblogfiles.naver.net%2F20140202_160%2Fpandorazbox7_1391333492146y5ovG_JPEG%2F201401_%25BD%25BA%25C6%25C4%25C0%25CC.JPG&amp;type=sc960_832</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20170607_7%2F1496812951145IU2Bn_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20150112_105%2F1421029834668IgXTx_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common/?src=http%3A%2F%2Fblogfiles.naver.net%2F20121024_49%2Fsunbono_1351052913136tQMKM_JPEG%2Fnaver_com_20121024_132008.jpg&amp;type=a340</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20111222_271%2F1324548307356l6aBt_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
+  </si>
+  <si>
+    <t>https://search.pstatic.net/common?type=o&amp;size=176x264&amp;quality=85&amp;direct=true&amp;src=https%3A%2F%2Fs.pstatic.net%2Fmovie.phinf%2F20200116_23%2F1579154974413LvtIf_JPEG%2Fmovie_image.jpg%3Ftype%3Dw640_2</t>
   </si>
 </sst>
 </file>
@@ -6551,12 +7840,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K493"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="35.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6591,7 +7880,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -6626,7 +7915,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6661,7 +7950,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -6696,7 +7985,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -6731,7 +8020,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -6766,7 +8055,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -6801,7 +8090,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -6836,7 +8125,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>46</v>
       </c>
@@ -6871,7 +8160,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -6906,7 +8195,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -6941,7 +8230,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -6976,7 +8265,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -7011,7 +8300,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -7046,7 +8335,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -7081,7 +8370,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>78</v>
       </c>
@@ -7116,7 +8405,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>83</v>
       </c>
@@ -7151,7 +8440,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -7186,7 +8475,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>93</v>
       </c>
@@ -7221,7 +8510,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -7256,7 +8545,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>103</v>
       </c>
@@ -7291,7 +8580,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>107</v>
       </c>
@@ -7326,7 +8615,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>111</v>
       </c>
@@ -7361,7 +8650,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>116</v>
       </c>
@@ -7396,7 +8685,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>119</v>
       </c>
@@ -7431,7 +8720,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>122</v>
       </c>
@@ -7466,7 +8755,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>127</v>
       </c>
@@ -7501,7 +8790,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>132</v>
       </c>
@@ -7536,7 +8825,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>136</v>
       </c>
@@ -7571,7 +8860,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>140</v>
       </c>
@@ -7606,7 +8895,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>145</v>
       </c>
@@ -7641,7 +8930,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>149</v>
       </c>
@@ -7676,7 +8965,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>153</v>
       </c>
@@ -7711,7 +9000,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>158</v>
       </c>
@@ -7746,7 +9035,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>163</v>
       </c>
@@ -7781,7 +9070,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>168</v>
       </c>
@@ -7816,7 +9105,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>173</v>
       </c>
@@ -7851,7 +9140,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>176</v>
       </c>
@@ -7886,7 +9175,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>181</v>
       </c>
@@ -7921,7 +9210,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>185</v>
       </c>
@@ -7956,7 +9245,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>188</v>
       </c>
@@ -7991,7 +9280,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>192</v>
       </c>
@@ -8026,7 +9315,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>196</v>
       </c>
@@ -8061,7 +9350,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>199</v>
       </c>
@@ -8096,7 +9385,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>203</v>
       </c>
@@ -8131,7 +9420,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>208</v>
       </c>
@@ -8166,7 +9455,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>211</v>
       </c>
@@ -8201,7 +9490,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>217</v>
       </c>
@@ -8236,7 +9525,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>222</v>
       </c>
@@ -8271,7 +9560,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>225</v>
       </c>
@@ -8306,7 +9595,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>230</v>
       </c>
@@ -8341,7 +9630,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>235</v>
       </c>
@@ -8376,7 +9665,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>240</v>
       </c>
@@ -8411,7 +9700,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>244</v>
       </c>
@@ -8446,7 +9735,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>247</v>
       </c>
@@ -8481,7 +9770,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>251</v>
       </c>
@@ -8516,7 +9805,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>256</v>
       </c>
@@ -8551,7 +9840,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>260</v>
       </c>
@@ -8586,7 +9875,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>263</v>
       </c>
@@ -8621,7 +9910,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>267</v>
       </c>
@@ -8656,7 +9945,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>270</v>
       </c>
@@ -8691,7 +9980,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>274</v>
       </c>
@@ -8726,7 +10015,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>277</v>
       </c>
@@ -8761,7 +10050,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>282</v>
       </c>
@@ -8796,7 +10085,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>287</v>
       </c>
@@ -8831,7 +10120,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>291</v>
       </c>
@@ -8866,7 +10155,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>295</v>
       </c>
@@ -8901,7 +10190,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>299</v>
       </c>
@@ -8936,7 +10225,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>304</v>
       </c>
@@ -8971,7 +10260,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>309</v>
       </c>
@@ -9006,7 +10295,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>313</v>
       </c>
@@ -9041,7 +10330,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>316</v>
       </c>
@@ -9076,7 +10365,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>320</v>
       </c>
@@ -9111,7 +10400,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>325</v>
       </c>
@@ -9146,7 +10435,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>329</v>
       </c>
@@ -9181,7 +10470,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>333</v>
       </c>
@@ -9216,7 +10505,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>337</v>
       </c>
@@ -9251,7 +10540,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>341</v>
       </c>
@@ -9286,7 +10575,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>344</v>
       </c>
@@ -9321,7 +10610,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>350</v>
       </c>
@@ -9356,7 +10645,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>354</v>
       </c>
@@ -9391,7 +10680,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>357</v>
       </c>
@@ -9426,7 +10715,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>363</v>
       </c>
@@ -9461,7 +10750,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>367</v>
       </c>
@@ -9496,7 +10785,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>371</v>
       </c>
@@ -9531,7 +10820,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>375</v>
       </c>
@@ -9566,7 +10855,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>380</v>
       </c>
@@ -9601,7 +10890,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>385</v>
       </c>
@@ -9636,7 +10925,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>390</v>
       </c>
@@ -9671,7 +10960,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>393</v>
       </c>
@@ -9706,7 +10995,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>396</v>
       </c>
@@ -9741,7 +11030,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>399</v>
       </c>
@@ -9776,7 +11065,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>404</v>
       </c>
@@ -9811,7 +11100,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>407</v>
       </c>
@@ -9846,7 +11135,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>412</v>
       </c>
@@ -9881,7 +11170,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>417</v>
       </c>
@@ -9916,7 +11205,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>421</v>
       </c>
@@ -9951,7 +11240,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>425</v>
       </c>
@@ -9986,7 +11275,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>429</v>
       </c>
@@ -10021,7 +11310,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>432</v>
       </c>
@@ -10056,7 +11345,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>437</v>
       </c>
@@ -10081,6 +11370,9 @@
       <c r="H101" t="s">
         <v>440</v>
       </c>
+      <c r="I101" t="s">
+        <v>2319</v>
+      </c>
       <c r="J101" t="s">
         <v>15</v>
       </c>
@@ -10088,7 +11380,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>441</v>
       </c>
@@ -10113,6 +11405,9 @@
       <c r="H102" t="s">
         <v>115</v>
       </c>
+      <c r="I102" t="s">
+        <v>2320</v>
+      </c>
       <c r="J102" t="s">
         <v>15</v>
       </c>
@@ -10120,7 +11415,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>444</v>
       </c>
@@ -10145,6 +11440,9 @@
       <c r="H103" t="s">
         <v>448</v>
       </c>
+      <c r="I103" t="s">
+        <v>2321</v>
+      </c>
       <c r="J103" t="s">
         <v>15</v>
       </c>
@@ -10152,7 +11450,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>449</v>
       </c>
@@ -10177,6 +11475,9 @@
       <c r="H104" t="s">
         <v>384</v>
       </c>
+      <c r="I104" t="s">
+        <v>2322</v>
+      </c>
       <c r="J104" t="s">
         <v>15</v>
       </c>
@@ -10184,7 +11485,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>452</v>
       </c>
@@ -10209,6 +11510,9 @@
       <c r="H105" t="s">
         <v>456</v>
       </c>
+      <c r="I105" t="s">
+        <v>2323</v>
+      </c>
       <c r="J105" t="s">
         <v>15</v>
       </c>
@@ -10216,7 +11520,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>457</v>
       </c>
@@ -10241,6 +11545,9 @@
       <c r="H106" t="s">
         <v>461</v>
       </c>
+      <c r="I106" t="s">
+        <v>2324</v>
+      </c>
       <c r="J106" t="s">
         <v>15</v>
       </c>
@@ -10248,7 +11555,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>462</v>
       </c>
@@ -10273,6 +11580,9 @@
       <c r="H107" t="s">
         <v>466</v>
       </c>
+      <c r="I107" t="s">
+        <v>2325</v>
+      </c>
       <c r="J107" t="s">
         <v>15</v>
       </c>
@@ -10280,7 +11590,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>467</v>
       </c>
@@ -10305,6 +11615,9 @@
       <c r="H108" t="s">
         <v>31</v>
       </c>
+      <c r="I108" t="s">
+        <v>2326</v>
+      </c>
       <c r="J108" t="s">
         <v>15</v>
       </c>
@@ -10312,7 +11625,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>470</v>
       </c>
@@ -10337,6 +11650,9 @@
       <c r="H109" t="s">
         <v>144</v>
       </c>
+      <c r="I109" t="s">
+        <v>2327</v>
+      </c>
       <c r="J109" t="s">
         <v>15</v>
       </c>
@@ -10344,7 +11660,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>473</v>
       </c>
@@ -10369,6 +11685,9 @@
       <c r="H110" t="s">
         <v>476</v>
       </c>
+      <c r="I110" t="s">
+        <v>2328</v>
+      </c>
       <c r="J110" t="s">
         <v>15</v>
       </c>
@@ -10376,7 +11695,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>477</v>
       </c>
@@ -10401,6 +11720,9 @@
       <c r="H111" t="s">
         <v>480</v>
       </c>
+      <c r="I111" t="s">
+        <v>2329</v>
+      </c>
       <c r="J111" t="s">
         <v>15</v>
       </c>
@@ -10408,7 +11730,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>481</v>
       </c>
@@ -10433,6 +11755,9 @@
       <c r="H112" t="s">
         <v>162</v>
       </c>
+      <c r="I112" t="s">
+        <v>2330</v>
+      </c>
       <c r="J112" t="s">
         <v>15</v>
       </c>
@@ -10440,7 +11765,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>484</v>
       </c>
@@ -10465,6 +11790,9 @@
       <c r="H113" t="s">
         <v>115</v>
       </c>
+      <c r="I113" t="s">
+        <v>2331</v>
+      </c>
       <c r="J113" t="s">
         <v>15</v>
       </c>
@@ -10472,7 +11800,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>487</v>
       </c>
@@ -10497,6 +11825,9 @@
       <c r="H114" t="s">
         <v>490</v>
       </c>
+      <c r="I114" t="s">
+        <v>2332</v>
+      </c>
       <c r="J114" t="s">
         <v>15</v>
       </c>
@@ -10504,7 +11835,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>491</v>
       </c>
@@ -10529,6 +11860,9 @@
       <c r="H115" t="s">
         <v>115</v>
       </c>
+      <c r="I115" t="s">
+        <v>2333</v>
+      </c>
       <c r="J115" t="s">
         <v>15</v>
       </c>
@@ -10536,7 +11870,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>494</v>
       </c>
@@ -10561,6 +11895,9 @@
       <c r="H116" t="s">
         <v>389</v>
       </c>
+      <c r="I116" t="s">
+        <v>2334</v>
+      </c>
       <c r="J116" t="s">
         <v>15</v>
       </c>
@@ -10568,7 +11905,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>498</v>
       </c>
@@ -10593,6 +11930,9 @@
       <c r="H117" t="s">
         <v>336</v>
       </c>
+      <c r="I117" t="s">
+        <v>2335</v>
+      </c>
       <c r="J117" t="s">
         <v>15</v>
       </c>
@@ -10600,7 +11940,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>501</v>
       </c>
@@ -10625,6 +11965,9 @@
       <c r="H118" t="s">
         <v>505</v>
       </c>
+      <c r="I118" t="s">
+        <v>2336</v>
+      </c>
       <c r="J118" t="s">
         <v>15</v>
       </c>
@@ -10632,7 +11975,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>506</v>
       </c>
@@ -10657,6 +12000,9 @@
       <c r="H119" t="s">
         <v>148</v>
       </c>
+      <c r="I119" t="s">
+        <v>2337</v>
+      </c>
       <c r="J119" t="s">
         <v>15</v>
       </c>
@@ -10664,7 +12010,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>509</v>
       </c>
@@ -10689,6 +12035,9 @@
       <c r="H120" t="s">
         <v>97</v>
       </c>
+      <c r="I120" t="s">
+        <v>2338</v>
+      </c>
       <c r="J120" t="s">
         <v>15</v>
       </c>
@@ -10696,7 +12045,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>513</v>
       </c>
@@ -10721,6 +12070,9 @@
       <c r="H121" t="s">
         <v>40</v>
       </c>
+      <c r="I121" t="s">
+        <v>2339</v>
+      </c>
       <c r="J121" t="s">
         <v>15</v>
       </c>
@@ -10728,7 +12080,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>516</v>
       </c>
@@ -10753,6 +12105,9 @@
       <c r="H122" t="s">
         <v>520</v>
       </c>
+      <c r="I122" t="s">
+        <v>2340</v>
+      </c>
       <c r="J122" t="s">
         <v>15</v>
       </c>
@@ -10760,7 +12115,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>521</v>
       </c>
@@ -10785,6 +12140,9 @@
       <c r="H123" t="s">
         <v>524</v>
       </c>
+      <c r="I123" t="s">
+        <v>2341</v>
+      </c>
       <c r="J123" t="s">
         <v>15</v>
       </c>
@@ -10792,7 +12150,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>525</v>
       </c>
@@ -10817,6 +12175,9 @@
       <c r="H124" t="s">
         <v>529</v>
       </c>
+      <c r="I124" t="s">
+        <v>2342</v>
+      </c>
       <c r="J124" t="s">
         <v>15</v>
       </c>
@@ -10824,7 +12185,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>530</v>
       </c>
@@ -10849,6 +12210,9 @@
       <c r="H125" t="s">
         <v>533</v>
       </c>
+      <c r="I125" t="s">
+        <v>2343</v>
+      </c>
       <c r="J125" t="s">
         <v>15</v>
       </c>
@@ -10856,7 +12220,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>534</v>
       </c>
@@ -10881,6 +12245,9 @@
       <c r="H126" t="s">
         <v>448</v>
       </c>
+      <c r="I126" t="s">
+        <v>2344</v>
+      </c>
       <c r="J126" t="s">
         <v>15</v>
       </c>
@@ -10888,7 +12255,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>538</v>
       </c>
@@ -10913,6 +12280,9 @@
       <c r="H127" t="s">
         <v>36</v>
       </c>
+      <c r="I127" t="s">
+        <v>2345</v>
+      </c>
       <c r="J127" t="s">
         <v>15</v>
       </c>
@@ -10920,7 +12290,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>541</v>
       </c>
@@ -10945,6 +12315,9 @@
       <c r="H128" t="s">
         <v>545</v>
       </c>
+      <c r="I128" t="s">
+        <v>2346</v>
+      </c>
       <c r="J128" t="s">
         <v>15</v>
       </c>
@@ -10952,7 +12325,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>546</v>
       </c>
@@ -10977,6 +12350,9 @@
       <c r="H129" t="s">
         <v>550</v>
       </c>
+      <c r="I129" t="s">
+        <v>2347</v>
+      </c>
       <c r="J129" t="s">
         <v>15</v>
       </c>
@@ -10984,7 +12360,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>551</v>
       </c>
@@ -11009,6 +12385,9 @@
       <c r="H130" t="s">
         <v>555</v>
       </c>
+      <c r="I130" t="s">
+        <v>2348</v>
+      </c>
       <c r="J130" t="s">
         <v>15</v>
       </c>
@@ -11016,7 +12395,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>556</v>
       </c>
@@ -11041,6 +12420,9 @@
       <c r="H131" t="s">
         <v>294</v>
       </c>
+      <c r="I131" t="s">
+        <v>2349</v>
+      </c>
       <c r="J131" t="s">
         <v>15</v>
       </c>
@@ -11048,7 +12430,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>559</v>
       </c>
@@ -11073,6 +12455,9 @@
       <c r="H132" t="s">
         <v>562</v>
       </c>
+      <c r="I132" t="s">
+        <v>2350</v>
+      </c>
       <c r="J132" t="s">
         <v>15</v>
       </c>
@@ -11080,7 +12465,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>563</v>
       </c>
@@ -11105,6 +12490,9 @@
       <c r="H133" t="s">
         <v>172</v>
       </c>
+      <c r="I133" t="s">
+        <v>2351</v>
+      </c>
       <c r="J133" t="s">
         <v>15</v>
       </c>
@@ -11112,7 +12500,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>567</v>
       </c>
@@ -11137,6 +12525,9 @@
       <c r="H134" t="s">
         <v>571</v>
       </c>
+      <c r="I134" t="s">
+        <v>2431</v>
+      </c>
       <c r="J134" t="s">
         <v>15</v>
       </c>
@@ -11144,7 +12535,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>572</v>
       </c>
@@ -11169,6 +12560,9 @@
       <c r="H135" t="s">
         <v>575</v>
       </c>
+      <c r="I135" t="s">
+        <v>2352</v>
+      </c>
       <c r="J135" t="s">
         <v>15</v>
       </c>
@@ -11176,7 +12570,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>576</v>
       </c>
@@ -11201,6 +12595,9 @@
       <c r="H136" t="s">
         <v>115</v>
       </c>
+      <c r="I136" t="s">
+        <v>2353</v>
+      </c>
       <c r="J136" t="s">
         <v>15</v>
       </c>
@@ -11208,7 +12605,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>580</v>
       </c>
@@ -11233,6 +12630,9 @@
       <c r="H137" t="s">
         <v>583</v>
       </c>
+      <c r="I137" t="s">
+        <v>2354</v>
+      </c>
       <c r="J137" t="s">
         <v>15</v>
       </c>
@@ -11240,7 +12640,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>584</v>
       </c>
@@ -11265,6 +12665,9 @@
       <c r="H138" t="s">
         <v>221</v>
       </c>
+      <c r="I138" t="s">
+        <v>2355</v>
+      </c>
       <c r="J138" t="s">
         <v>15</v>
       </c>
@@ -11272,7 +12675,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>588</v>
       </c>
@@ -11297,6 +12700,9 @@
       <c r="H139" t="s">
         <v>591</v>
       </c>
+      <c r="I139" t="s">
+        <v>2356</v>
+      </c>
       <c r="J139" t="s">
         <v>15</v>
       </c>
@@ -11304,7 +12710,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>592</v>
       </c>
@@ -11329,6 +12735,9 @@
       <c r="H140" t="s">
         <v>596</v>
       </c>
+      <c r="I140" t="s">
+        <v>2357</v>
+      </c>
       <c r="J140" t="s">
         <v>15</v>
       </c>
@@ -11336,7 +12745,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>597</v>
       </c>
@@ -11361,6 +12770,9 @@
       <c r="H141" t="s">
         <v>600</v>
       </c>
+      <c r="I141" t="s">
+        <v>2358</v>
+      </c>
       <c r="J141" t="s">
         <v>15</v>
       </c>
@@ -11368,7 +12780,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>601</v>
       </c>
@@ -11393,6 +12805,9 @@
       <c r="H142" t="s">
         <v>604</v>
       </c>
+      <c r="I142" t="s">
+        <v>2359</v>
+      </c>
       <c r="J142" t="s">
         <v>15</v>
       </c>
@@ -11400,7 +12815,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>605</v>
       </c>
@@ -11425,6 +12840,9 @@
       <c r="H143" t="s">
         <v>31</v>
       </c>
+      <c r="I143" t="s">
+        <v>2360</v>
+      </c>
       <c r="J143" t="s">
         <v>15</v>
       </c>
@@ -11432,7 +12850,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>609</v>
       </c>
@@ -11457,6 +12875,9 @@
       <c r="H144" t="s">
         <v>448</v>
       </c>
+      <c r="I144" t="s">
+        <v>2361</v>
+      </c>
       <c r="J144" t="s">
         <v>15</v>
       </c>
@@ -11464,7 +12885,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>613</v>
       </c>
@@ -11489,6 +12910,9 @@
       <c r="H145" t="s">
         <v>403</v>
       </c>
+      <c r="I145" t="s">
+        <v>2362</v>
+      </c>
       <c r="J145" t="s">
         <v>15</v>
       </c>
@@ -11496,7 +12920,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>616</v>
       </c>
@@ -11521,6 +12945,9 @@
       <c r="H146" t="s">
         <v>620</v>
       </c>
+      <c r="I146" t="s">
+        <v>2363</v>
+      </c>
       <c r="J146" t="s">
         <v>15</v>
       </c>
@@ -11528,7 +12955,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>621</v>
       </c>
@@ -11553,6 +12980,9 @@
       <c r="H147" t="s">
         <v>624</v>
       </c>
+      <c r="I147" t="s">
+        <v>2364</v>
+      </c>
       <c r="J147" t="s">
         <v>15</v>
       </c>
@@ -11560,7 +12990,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>625</v>
       </c>
@@ -11585,6 +13015,9 @@
       <c r="H148" t="s">
         <v>26</v>
       </c>
+      <c r="I148" t="s">
+        <v>2365</v>
+      </c>
       <c r="J148" t="s">
         <v>15</v>
       </c>
@@ -11592,7 +13025,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>628</v>
       </c>
@@ -11617,6 +13050,9 @@
       <c r="H149" t="s">
         <v>180</v>
       </c>
+      <c r="I149" t="s">
+        <v>2366</v>
+      </c>
       <c r="J149" t="s">
         <v>15</v>
       </c>
@@ -11624,7 +13060,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>632</v>
       </c>
@@ -11649,6 +13085,9 @@
       <c r="H150" t="s">
         <v>635</v>
       </c>
+      <c r="I150" t="s">
+        <v>2367</v>
+      </c>
       <c r="J150" t="s">
         <v>15</v>
       </c>
@@ -11656,7 +13095,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>636</v>
       </c>
@@ -11681,6 +13120,9 @@
       <c r="H151" t="s">
         <v>639</v>
       </c>
+      <c r="I151" t="s">
+        <v>2368</v>
+      </c>
       <c r="J151" t="s">
         <v>15</v>
       </c>
@@ -11688,7 +13130,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>640</v>
       </c>
@@ -11713,6 +13155,9 @@
       <c r="H152" t="s">
         <v>550</v>
       </c>
+      <c r="I152" t="s">
+        <v>2369</v>
+      </c>
       <c r="J152" t="s">
         <v>15</v>
       </c>
@@ -11720,7 +13165,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>643</v>
       </c>
@@ -11745,6 +13190,9 @@
       <c r="H153" t="s">
         <v>646</v>
       </c>
+      <c r="I153" t="s">
+        <v>2370</v>
+      </c>
       <c r="J153" t="s">
         <v>15</v>
       </c>
@@ -11752,7 +13200,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>647</v>
       </c>
@@ -11777,6 +13225,9 @@
       <c r="H154" t="s">
         <v>520</v>
       </c>
+      <c r="I154" t="s">
+        <v>2371</v>
+      </c>
       <c r="J154" t="s">
         <v>15</v>
       </c>
@@ -11784,7 +13235,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>651</v>
       </c>
@@ -11809,6 +13260,9 @@
       <c r="H155" t="s">
         <v>654</v>
       </c>
+      <c r="I155" t="s">
+        <v>2372</v>
+      </c>
       <c r="J155" t="s">
         <v>15</v>
       </c>
@@ -11816,7 +13270,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>655</v>
       </c>
@@ -11841,6 +13295,9 @@
       <c r="H156" t="s">
         <v>69</v>
       </c>
+      <c r="I156" t="s">
+        <v>2373</v>
+      </c>
       <c r="J156" t="s">
         <v>15</v>
       </c>
@@ -11848,7 +13305,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>658</v>
       </c>
@@ -11873,6 +13330,9 @@
       <c r="H157" t="s">
         <v>661</v>
       </c>
+      <c r="I157" t="s">
+        <v>2374</v>
+      </c>
       <c r="J157" t="s">
         <v>15</v>
       </c>
@@ -11880,7 +13340,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>662</v>
       </c>
@@ -11905,6 +13365,9 @@
       <c r="H158" t="s">
         <v>665</v>
       </c>
+      <c r="I158" t="s">
+        <v>2375</v>
+      </c>
       <c r="J158" t="s">
         <v>15</v>
       </c>
@@ -11912,7 +13375,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>666</v>
       </c>
@@ -11937,6 +13400,9 @@
       <c r="H159" t="s">
         <v>635</v>
       </c>
+      <c r="I159" t="s">
+        <v>2376</v>
+      </c>
       <c r="J159" t="s">
         <v>15</v>
       </c>
@@ -11944,7 +13410,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>670</v>
       </c>
@@ -11969,6 +13435,9 @@
       <c r="H160" t="s">
         <v>20</v>
       </c>
+      <c r="I160" t="s">
+        <v>2377</v>
+      </c>
       <c r="J160" t="s">
         <v>15</v>
       </c>
@@ -11976,7 +13445,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>674</v>
       </c>
@@ -12001,6 +13470,9 @@
       <c r="H161" t="s">
         <v>677</v>
       </c>
+      <c r="I161" t="s">
+        <v>2378</v>
+      </c>
       <c r="J161" t="s">
         <v>15</v>
       </c>
@@ -12008,7 +13480,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>678</v>
       </c>
@@ -12033,6 +13505,9 @@
       <c r="H162" t="s">
         <v>682</v>
       </c>
+      <c r="I162" t="s">
+        <v>2379</v>
+      </c>
       <c r="J162" t="s">
         <v>15</v>
       </c>
@@ -12040,7 +13515,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>683</v>
       </c>
@@ -12065,6 +13540,9 @@
       <c r="H163" t="s">
         <v>45</v>
       </c>
+      <c r="I163" t="s">
+        <v>2380</v>
+      </c>
       <c r="J163" t="s">
         <v>15</v>
       </c>
@@ -12072,7 +13550,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>686</v>
       </c>
@@ -12097,6 +13575,9 @@
       <c r="H164" t="s">
         <v>690</v>
       </c>
+      <c r="I164" t="s">
+        <v>2381</v>
+      </c>
       <c r="J164" t="s">
         <v>15</v>
       </c>
@@ -12104,7 +13585,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>691</v>
       </c>
@@ -12129,6 +13610,9 @@
       <c r="H165" t="s">
         <v>461</v>
       </c>
+      <c r="I165" t="s">
+        <v>2382</v>
+      </c>
       <c r="J165" t="s">
         <v>15</v>
       </c>
@@ -12136,7 +13620,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>694</v>
       </c>
@@ -12161,6 +13645,9 @@
       <c r="H166" t="s">
         <v>697</v>
       </c>
+      <c r="I166" t="s">
+        <v>2383</v>
+      </c>
       <c r="J166" t="s">
         <v>15</v>
       </c>
@@ -12168,7 +13655,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>698</v>
       </c>
@@ -12193,6 +13680,9 @@
       <c r="H167" t="s">
         <v>701</v>
       </c>
+      <c r="I167" t="s">
+        <v>2384</v>
+      </c>
       <c r="J167" t="s">
         <v>15</v>
       </c>
@@ -12200,7 +13690,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>702</v>
       </c>
@@ -12225,6 +13715,9 @@
       <c r="H168" t="s">
         <v>82</v>
       </c>
+      <c r="I168" t="s">
+        <v>2385</v>
+      </c>
       <c r="J168" t="s">
         <v>15</v>
       </c>
@@ -12232,7 +13725,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>705</v>
       </c>
@@ -12257,6 +13750,9 @@
       <c r="H169" t="s">
         <v>708</v>
       </c>
+      <c r="I169" t="s">
+        <v>2386</v>
+      </c>
       <c r="J169" t="s">
         <v>15</v>
       </c>
@@ -12264,7 +13760,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>709</v>
       </c>
@@ -12289,6 +13785,9 @@
       <c r="H170" t="s">
         <v>713</v>
       </c>
+      <c r="I170" t="s">
+        <v>2387</v>
+      </c>
       <c r="J170" t="s">
         <v>15</v>
       </c>
@@ -12296,7 +13795,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>714</v>
       </c>
@@ -12321,6 +13820,9 @@
       <c r="H171" t="s">
         <v>717</v>
       </c>
+      <c r="I171" t="s">
+        <v>2388</v>
+      </c>
       <c r="J171" t="s">
         <v>15</v>
       </c>
@@ -12328,7 +13830,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>718</v>
       </c>
@@ -12353,6 +13855,9 @@
       <c r="H172" t="s">
         <v>654</v>
       </c>
+      <c r="I172" t="s">
+        <v>2389</v>
+      </c>
       <c r="J172" t="s">
         <v>15</v>
       </c>
@@ -12360,7 +13865,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>722</v>
       </c>
@@ -12385,6 +13890,9 @@
       <c r="H173" t="s">
         <v>725</v>
       </c>
+      <c r="I173" t="s">
+        <v>2390</v>
+      </c>
       <c r="J173" t="s">
         <v>15</v>
       </c>
@@ -12392,7 +13900,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>726</v>
       </c>
@@ -12417,6 +13925,9 @@
       <c r="H174" t="s">
         <v>461</v>
       </c>
+      <c r="I174" t="s">
+        <v>2391</v>
+      </c>
       <c r="J174" t="s">
         <v>15</v>
       </c>
@@ -12424,7 +13935,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>730</v>
       </c>
@@ -12449,6 +13960,9 @@
       <c r="H175" t="s">
         <v>733</v>
       </c>
+      <c r="I175" t="s">
+        <v>2392</v>
+      </c>
       <c r="J175" t="s">
         <v>15</v>
       </c>
@@ -12456,7 +13970,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>734</v>
       </c>
@@ -12481,6 +13995,9 @@
       <c r="H176" t="s">
         <v>737</v>
       </c>
+      <c r="I176" t="s">
+        <v>2393</v>
+      </c>
       <c r="J176" t="s">
         <v>15</v>
       </c>
@@ -12488,7 +14005,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>738</v>
       </c>
@@ -12513,6 +14030,9 @@
       <c r="H177" t="s">
         <v>403</v>
       </c>
+      <c r="I177" t="s">
+        <v>2394</v>
+      </c>
       <c r="J177" t="s">
         <v>15</v>
       </c>
@@ -12520,7 +14040,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>741</v>
       </c>
@@ -12545,6 +14065,9 @@
       <c r="H178" t="s">
         <v>73</v>
       </c>
+      <c r="I178" t="s">
+        <v>2395</v>
+      </c>
       <c r="J178" t="s">
         <v>15</v>
       </c>
@@ -12552,7 +14075,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>745</v>
       </c>
@@ -12577,6 +14100,9 @@
       <c r="H179" t="s">
         <v>36</v>
       </c>
+      <c r="I179" t="s">
+        <v>2396</v>
+      </c>
       <c r="J179" t="s">
         <v>15</v>
       </c>
@@ -12584,7 +14110,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>748</v>
       </c>
@@ -12609,6 +14135,9 @@
       <c r="H180" t="s">
         <v>31</v>
       </c>
+      <c r="I180" t="s">
+        <v>2397</v>
+      </c>
       <c r="J180" t="s">
         <v>15</v>
       </c>
@@ -12616,7 +14145,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>751</v>
       </c>
@@ -12641,6 +14170,9 @@
       <c r="H181" t="s">
         <v>604</v>
       </c>
+      <c r="I181" t="s">
+        <v>2398</v>
+      </c>
       <c r="J181" t="s">
         <v>15</v>
       </c>
@@ -12648,7 +14180,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>754</v>
       </c>
@@ -12673,6 +14205,9 @@
       <c r="H182" t="s">
         <v>758</v>
       </c>
+      <c r="I182" t="s">
+        <v>2399</v>
+      </c>
       <c r="J182" t="s">
         <v>15</v>
       </c>
@@ -12680,7 +14215,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>759</v>
       </c>
@@ -12705,6 +14240,9 @@
       <c r="H183" t="s">
         <v>73</v>
       </c>
+      <c r="I183" t="s">
+        <v>2400</v>
+      </c>
       <c r="J183" t="s">
         <v>15</v>
       </c>
@@ -12712,7 +14250,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>762</v>
       </c>
@@ -12737,6 +14275,9 @@
       <c r="H184" t="s">
         <v>461</v>
       </c>
+      <c r="I184" t="s">
+        <v>2401</v>
+      </c>
       <c r="J184" t="s">
         <v>15</v>
       </c>
@@ -12744,7 +14285,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>765</v>
       </c>
@@ -12769,6 +14310,9 @@
       <c r="H185" t="s">
         <v>768</v>
       </c>
+      <c r="I185" t="s">
+        <v>2402</v>
+      </c>
       <c r="J185" t="s">
         <v>15</v>
       </c>
@@ -12776,7 +14320,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>769</v>
       </c>
@@ -12801,6 +14345,9 @@
       <c r="H186" t="s">
         <v>384</v>
       </c>
+      <c r="I186" t="s">
+        <v>2403</v>
+      </c>
       <c r="J186" t="s">
         <v>15</v>
       </c>
@@ -12808,7 +14355,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>773</v>
       </c>
@@ -12833,6 +14380,9 @@
       <c r="H187" t="s">
         <v>777</v>
       </c>
+      <c r="I187" t="s">
+        <v>2404</v>
+      </c>
       <c r="J187" t="s">
         <v>15</v>
       </c>
@@ -12840,7 +14390,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>778</v>
       </c>
@@ -12865,6 +14415,9 @@
       <c r="H188" t="s">
         <v>782</v>
       </c>
+      <c r="I188" t="s">
+        <v>2405</v>
+      </c>
       <c r="J188" t="s">
         <v>15</v>
       </c>
@@ -12872,7 +14425,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>783</v>
       </c>
@@ -12897,6 +14450,9 @@
       <c r="H189" t="s">
         <v>786</v>
       </c>
+      <c r="I189" t="s">
+        <v>2406</v>
+      </c>
       <c r="J189" t="s">
         <v>15</v>
       </c>
@@ -12904,7 +14460,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>787</v>
       </c>
@@ -12929,6 +14485,9 @@
       <c r="H190" t="s">
         <v>790</v>
       </c>
+      <c r="I190" t="s">
+        <v>2407</v>
+      </c>
       <c r="J190" t="s">
         <v>15</v>
       </c>
@@ -12936,7 +14495,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>791</v>
       </c>
@@ -12961,6 +14520,9 @@
       <c r="H191" t="s">
         <v>646</v>
       </c>
+      <c r="I191" t="s">
+        <v>2408</v>
+      </c>
       <c r="J191" t="s">
         <v>15</v>
       </c>
@@ -12968,7 +14530,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>794</v>
       </c>
@@ -12993,6 +14555,9 @@
       <c r="H192" t="s">
         <v>797</v>
       </c>
+      <c r="I192" t="s">
+        <v>2409</v>
+      </c>
       <c r="J192" t="s">
         <v>15</v>
       </c>
@@ -13000,7 +14565,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>798</v>
       </c>
@@ -13025,6 +14590,9 @@
       <c r="H193" t="s">
         <v>801</v>
       </c>
+      <c r="I193" t="s">
+        <v>2410</v>
+      </c>
       <c r="J193" t="s">
         <v>15</v>
       </c>
@@ -13032,7 +14600,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>802</v>
       </c>
@@ -13057,6 +14625,9 @@
       <c r="H194" t="s">
         <v>682</v>
       </c>
+      <c r="I194" t="s">
+        <v>2411</v>
+      </c>
       <c r="J194" t="s">
         <v>15</v>
       </c>
@@ -13064,7 +14635,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>806</v>
       </c>
@@ -13089,6 +14660,9 @@
       <c r="H195" t="s">
         <v>221</v>
       </c>
+      <c r="I195" t="s">
+        <v>2412</v>
+      </c>
       <c r="J195" t="s">
         <v>15</v>
       </c>
@@ -13096,7 +14670,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>809</v>
       </c>
@@ -13121,6 +14695,9 @@
       <c r="H196" t="s">
         <v>812</v>
       </c>
+      <c r="I196" t="s">
+        <v>2413</v>
+      </c>
       <c r="J196" t="s">
         <v>15</v>
       </c>
@@ -13128,7 +14705,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>813</v>
       </c>
@@ -13153,6 +14730,9 @@
       <c r="H197" t="s">
         <v>332</v>
       </c>
+      <c r="I197" t="s">
+        <v>2414</v>
+      </c>
       <c r="J197" t="s">
         <v>15</v>
       </c>
@@ -13160,7 +14740,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>817</v>
       </c>
@@ -13185,6 +14765,9 @@
       <c r="H198" t="s">
         <v>411</v>
       </c>
+      <c r="I198" t="s">
+        <v>2415</v>
+      </c>
       <c r="J198" t="s">
         <v>15</v>
       </c>
@@ -13192,7 +14775,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>821</v>
       </c>
@@ -13217,6 +14800,9 @@
       <c r="H199" t="s">
         <v>824</v>
       </c>
+      <c r="I199" t="s">
+        <v>2416</v>
+      </c>
       <c r="J199" t="s">
         <v>15</v>
       </c>
@@ -13224,7 +14810,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>825</v>
       </c>
@@ -13249,6 +14835,9 @@
       <c r="H200" t="s">
         <v>167</v>
       </c>
+      <c r="I200" t="s">
+        <v>2417</v>
+      </c>
       <c r="J200" t="s">
         <v>15</v>
       </c>
@@ -13256,7 +14845,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>828</v>
       </c>
@@ -13281,6 +14870,9 @@
       <c r="H201" t="s">
         <v>448</v>
       </c>
+      <c r="I201" s="2" t="s">
+        <v>2045</v>
+      </c>
       <c r="J201" t="s">
         <v>15</v>
       </c>
@@ -13288,7 +14880,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>832</v>
       </c>
@@ -13313,6 +14905,9 @@
       <c r="H202" t="s">
         <v>562</v>
       </c>
+      <c r="I202" s="2" t="s">
+        <v>2046</v>
+      </c>
       <c r="J202" t="s">
         <v>15</v>
       </c>
@@ -13320,7 +14915,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>835</v>
       </c>
@@ -13345,6 +14940,9 @@
       <c r="H203" t="s">
         <v>839</v>
       </c>
+      <c r="I203" s="2" t="s">
+        <v>2047</v>
+      </c>
       <c r="J203" t="s">
         <v>15</v>
       </c>
@@ -13352,7 +14950,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>840</v>
       </c>
@@ -13377,6 +14975,9 @@
       <c r="H204" t="s">
         <v>844</v>
       </c>
+      <c r="I204" s="2" t="s">
+        <v>2048</v>
+      </c>
       <c r="J204" t="s">
         <v>15</v>
       </c>
@@ -13384,7 +14985,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>845</v>
       </c>
@@ -13409,6 +15010,9 @@
       <c r="H205" t="s">
         <v>801</v>
       </c>
+      <c r="I205" s="2" t="s">
+        <v>2049</v>
+      </c>
       <c r="J205" t="s">
         <v>15</v>
       </c>
@@ -13416,7 +15020,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>849</v>
       </c>
@@ -13441,6 +15045,9 @@
       <c r="H206" t="s">
         <v>852</v>
       </c>
+      <c r="I206" s="2" t="s">
+        <v>2050</v>
+      </c>
       <c r="J206" t="s">
         <v>15</v>
       </c>
@@ -13448,7 +15055,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>853</v>
       </c>
@@ -13473,6 +15080,9 @@
       <c r="H207" t="s">
         <v>389</v>
       </c>
+      <c r="I207" s="2" t="s">
+        <v>2051</v>
+      </c>
       <c r="J207" t="s">
         <v>15</v>
       </c>
@@ -13480,7 +15090,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>856</v>
       </c>
@@ -13505,6 +15115,9 @@
       <c r="H208" t="s">
         <v>860</v>
       </c>
+      <c r="I208" s="2" t="s">
+        <v>2052</v>
+      </c>
       <c r="J208" t="s">
         <v>15</v>
       </c>
@@ -13512,7 +15125,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>861</v>
       </c>
@@ -13537,6 +15150,9 @@
       <c r="H209" t="s">
         <v>864</v>
       </c>
+      <c r="I209" s="2" t="s">
+        <v>2053</v>
+      </c>
       <c r="J209" t="s">
         <v>15</v>
       </c>
@@ -13544,7 +15160,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>865</v>
       </c>
@@ -13569,6 +15185,9 @@
       <c r="H210" t="s">
         <v>604</v>
       </c>
+      <c r="I210" s="2" t="s">
+        <v>2054</v>
+      </c>
       <c r="J210" t="s">
         <v>15</v>
       </c>
@@ -13576,7 +15195,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>868</v>
       </c>
@@ -13601,6 +15220,9 @@
       <c r="H211" t="s">
         <v>871</v>
       </c>
+      <c r="I211" s="2" t="s">
+        <v>2055</v>
+      </c>
       <c r="J211" t="s">
         <v>15</v>
       </c>
@@ -13608,7 +15230,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>872</v>
       </c>
@@ -13633,6 +15255,9 @@
       <c r="H212" t="s">
         <v>876</v>
       </c>
+      <c r="I212" s="2" t="s">
+        <v>2056</v>
+      </c>
       <c r="J212" t="s">
         <v>15</v>
       </c>
@@ -13640,7 +15265,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>877</v>
       </c>
@@ -13665,6 +15290,9 @@
       <c r="H213" t="s">
         <v>87</v>
       </c>
+      <c r="I213" s="2" t="s">
+        <v>2057</v>
+      </c>
       <c r="J213" t="s">
         <v>15</v>
       </c>
@@ -13672,7 +15300,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>880</v>
       </c>
@@ -13697,6 +15325,9 @@
       <c r="H214" t="s">
         <v>198</v>
       </c>
+      <c r="I214" s="2" t="s">
+        <v>2058</v>
+      </c>
       <c r="J214" t="s">
         <v>15</v>
       </c>
@@ -13704,7 +15335,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>884</v>
       </c>
@@ -13729,6 +15360,9 @@
       <c r="H215" t="s">
         <v>887</v>
       </c>
+      <c r="I215" s="2" t="s">
+        <v>2059</v>
+      </c>
       <c r="J215" t="s">
         <v>15</v>
       </c>
@@ -13736,7 +15370,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>888</v>
       </c>
@@ -13761,7 +15395,9 @@
       <c r="H216" t="s">
         <v>891</v>
       </c>
-      <c r="I216" s="2"/>
+      <c r="I216" s="2" t="s">
+        <v>2060</v>
+      </c>
       <c r="J216" t="s">
         <v>15</v>
       </c>
@@ -13769,7 +15405,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>892</v>
       </c>
@@ -13794,6 +15430,9 @@
       <c r="H217" t="s">
         <v>895</v>
       </c>
+      <c r="I217" s="2" t="s">
+        <v>2061</v>
+      </c>
       <c r="J217" t="s">
         <v>15</v>
       </c>
@@ -13801,7 +15440,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>896</v>
       </c>
@@ -13826,6 +15465,9 @@
       <c r="H218" t="s">
         <v>73</v>
       </c>
+      <c r="I218" s="2" t="s">
+        <v>2432</v>
+      </c>
       <c r="J218" t="s">
         <v>15</v>
       </c>
@@ -13833,7 +15475,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>900</v>
       </c>
@@ -13858,6 +15500,9 @@
       <c r="H219" t="s">
         <v>904</v>
       </c>
+      <c r="I219" s="2" t="s">
+        <v>2062</v>
+      </c>
       <c r="J219" t="s">
         <v>15</v>
       </c>
@@ -13865,7 +15510,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>905</v>
       </c>
@@ -13890,6 +15535,9 @@
       <c r="H220" t="s">
         <v>909</v>
       </c>
+      <c r="I220" s="2" t="s">
+        <v>2063</v>
+      </c>
       <c r="J220" t="s">
         <v>15</v>
       </c>
@@ -13897,7 +15545,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>910</v>
       </c>
@@ -13922,6 +15570,9 @@
       <c r="H221" t="s">
         <v>913</v>
       </c>
+      <c r="I221" s="2" t="s">
+        <v>2064</v>
+      </c>
       <c r="J221" t="s">
         <v>15</v>
       </c>
@@ -13929,7 +15580,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>914</v>
       </c>
@@ -13954,6 +15605,9 @@
       <c r="H222" t="s">
         <v>917</v>
       </c>
+      <c r="I222" s="2" t="s">
+        <v>2065</v>
+      </c>
       <c r="J222" t="s">
         <v>15</v>
       </c>
@@ -13961,7 +15615,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>918</v>
       </c>
@@ -13986,6 +15640,9 @@
       <c r="H223" t="s">
         <v>677</v>
       </c>
+      <c r="I223" s="2" t="s">
+        <v>2066</v>
+      </c>
       <c r="J223" t="s">
         <v>15</v>
       </c>
@@ -13993,7 +15650,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>922</v>
       </c>
@@ -14018,6 +15675,9 @@
       <c r="H224" t="s">
         <v>926</v>
       </c>
+      <c r="I224" s="2" t="s">
+        <v>2067</v>
+      </c>
       <c r="J224" t="s">
         <v>927</v>
       </c>
@@ -14025,7 +15685,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>928</v>
       </c>
@@ -14050,6 +15710,9 @@
       <c r="H225" t="s">
         <v>654</v>
       </c>
+      <c r="I225" s="2" t="s">
+        <v>2068</v>
+      </c>
       <c r="J225" t="s">
         <v>15</v>
       </c>
@@ -14057,7 +15720,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>931</v>
       </c>
@@ -14082,6 +15745,9 @@
       <c r="H226" t="s">
         <v>934</v>
       </c>
+      <c r="I226" s="2" t="s">
+        <v>2069</v>
+      </c>
       <c r="J226" t="s">
         <v>15</v>
       </c>
@@ -14089,7 +15755,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>935</v>
       </c>
@@ -14114,6 +15780,9 @@
       <c r="H227" t="s">
         <v>939</v>
       </c>
+      <c r="I227" s="2" t="s">
+        <v>2070</v>
+      </c>
       <c r="J227" t="s">
         <v>15</v>
       </c>
@@ -14121,7 +15790,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>940</v>
       </c>
@@ -14146,6 +15815,9 @@
       <c r="H228" t="s">
         <v>777</v>
       </c>
+      <c r="I228" s="2" t="s">
+        <v>2071</v>
+      </c>
       <c r="J228" t="s">
         <v>15</v>
       </c>
@@ -14153,7 +15825,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>944</v>
       </c>
@@ -14178,6 +15850,9 @@
       <c r="H229" t="s">
         <v>14</v>
       </c>
+      <c r="I229" s="2" t="s">
+        <v>2072</v>
+      </c>
       <c r="J229" t="s">
         <v>15</v>
       </c>
@@ -14185,7 +15860,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>948</v>
       </c>
@@ -14210,6 +15885,9 @@
       <c r="H230" t="s">
         <v>951</v>
       </c>
+      <c r="I230" s="2" t="s">
+        <v>2073</v>
+      </c>
       <c r="J230" t="s">
         <v>15</v>
       </c>
@@ -14217,7 +15895,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>952</v>
       </c>
@@ -14242,6 +15920,9 @@
       <c r="H231" t="s">
         <v>191</v>
       </c>
+      <c r="I231" s="2" t="s">
+        <v>2074</v>
+      </c>
       <c r="J231" t="s">
         <v>15</v>
       </c>
@@ -14249,7 +15930,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>956</v>
       </c>
@@ -14274,6 +15955,9 @@
       <c r="H232" t="s">
         <v>448</v>
       </c>
+      <c r="I232" s="2" t="s">
+        <v>2075</v>
+      </c>
       <c r="J232" t="s">
         <v>15</v>
       </c>
@@ -14281,7 +15965,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>960</v>
       </c>
@@ -14306,6 +15990,9 @@
       <c r="H233" t="s">
         <v>963</v>
       </c>
+      <c r="I233" s="2" t="s">
+        <v>2076</v>
+      </c>
       <c r="J233" t="s">
         <v>15</v>
       </c>
@@ -14313,7 +16000,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>964</v>
       </c>
@@ -14338,6 +16025,9 @@
       <c r="H234" t="s">
         <v>968</v>
       </c>
+      <c r="I234" s="2" t="s">
+        <v>2077</v>
+      </c>
       <c r="J234" t="s">
         <v>15</v>
       </c>
@@ -14345,7 +16035,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>969</v>
       </c>
@@ -14370,6 +16060,9 @@
       <c r="H235" t="s">
         <v>973</v>
       </c>
+      <c r="I235" s="2" t="s">
+        <v>2078</v>
+      </c>
       <c r="J235" t="s">
         <v>15</v>
       </c>
@@ -14377,7 +16070,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>974</v>
       </c>
@@ -14402,6 +16095,9 @@
       <c r="H236" t="s">
         <v>977</v>
       </c>
+      <c r="I236" s="2" t="s">
+        <v>2079</v>
+      </c>
       <c r="J236" t="s">
         <v>15</v>
       </c>
@@ -14409,7 +16105,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>978</v>
       </c>
@@ -14434,6 +16130,9 @@
       <c r="H237" t="s">
         <v>981</v>
       </c>
+      <c r="I237" s="2" t="s">
+        <v>2080</v>
+      </c>
       <c r="J237" t="s">
         <v>15</v>
       </c>
@@ -14441,7 +16140,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>982</v>
       </c>
@@ -14466,6 +16165,9 @@
       <c r="H238" t="s">
         <v>191</v>
       </c>
+      <c r="I238" s="2" t="s">
+        <v>2081</v>
+      </c>
       <c r="J238" t="s">
         <v>15</v>
       </c>
@@ -14473,7 +16175,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>985</v>
       </c>
@@ -14498,6 +16200,9 @@
       <c r="H239" t="s">
         <v>988</v>
       </c>
+      <c r="I239" s="2" t="s">
+        <v>2082</v>
+      </c>
       <c r="J239" t="s">
         <v>15</v>
       </c>
@@ -14505,7 +16210,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>989</v>
       </c>
@@ -14530,6 +16235,9 @@
       <c r="H240" t="s">
         <v>520</v>
       </c>
+      <c r="I240" s="2" t="s">
+        <v>2433</v>
+      </c>
       <c r="J240" t="s">
         <v>15</v>
       </c>
@@ -14537,7 +16245,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>992</v>
       </c>
@@ -14562,6 +16270,9 @@
       <c r="H241" t="s">
         <v>995</v>
       </c>
+      <c r="I241" s="2" t="s">
+        <v>2083</v>
+      </c>
       <c r="J241" t="s">
         <v>15</v>
       </c>
@@ -14569,7 +16280,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>996</v>
       </c>
@@ -14594,6 +16305,9 @@
       <c r="H242" t="s">
         <v>40</v>
       </c>
+      <c r="I242" s="2" t="s">
+        <v>2084</v>
+      </c>
       <c r="J242" t="s">
         <v>15</v>
       </c>
@@ -14601,7 +16315,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>1000</v>
       </c>
@@ -14626,6 +16340,9 @@
       <c r="H243" t="s">
         <v>239</v>
       </c>
+      <c r="I243" s="2" t="s">
+        <v>2085</v>
+      </c>
       <c r="J243" t="s">
         <v>15</v>
       </c>
@@ -14633,7 +16350,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>1004</v>
       </c>
@@ -14658,6 +16375,9 @@
       <c r="H244" t="s">
         <v>1007</v>
       </c>
+      <c r="I244" s="2" t="s">
+        <v>2086</v>
+      </c>
       <c r="J244" t="s">
         <v>15</v>
       </c>
@@ -14665,7 +16385,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>1008</v>
       </c>
@@ -14690,6 +16410,9 @@
       <c r="H245" t="s">
         <v>1012</v>
       </c>
+      <c r="I245" s="2" t="s">
+        <v>2087</v>
+      </c>
       <c r="J245" t="s">
         <v>15</v>
       </c>
@@ -14697,7 +16420,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>1013</v>
       </c>
@@ -14722,6 +16445,9 @@
       <c r="H246" t="s">
         <v>635</v>
       </c>
+      <c r="I246" s="2" t="s">
+        <v>2088</v>
+      </c>
       <c r="J246" t="s">
         <v>15</v>
       </c>
@@ -14729,7 +16455,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>1016</v>
       </c>
@@ -14754,6 +16480,9 @@
       <c r="H247" t="s">
         <v>1019</v>
       </c>
+      <c r="I247" s="2" t="s">
+        <v>2089</v>
+      </c>
       <c r="J247" t="s">
         <v>15</v>
       </c>
@@ -14761,7 +16490,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>1020</v>
       </c>
@@ -14786,6 +16515,9 @@
       <c r="H248" t="s">
         <v>92</v>
       </c>
+      <c r="I248" s="2" t="s">
+        <v>2090</v>
+      </c>
       <c r="J248" t="s">
         <v>15</v>
       </c>
@@ -14793,7 +16525,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>1024</v>
       </c>
@@ -14818,6 +16550,9 @@
       <c r="H249" t="s">
         <v>1027</v>
       </c>
+      <c r="I249" s="2" t="s">
+        <v>2091</v>
+      </c>
       <c r="J249" t="s">
         <v>15</v>
       </c>
@@ -14825,7 +16560,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>1028</v>
       </c>
@@ -14850,6 +16585,9 @@
       <c r="H250" t="s">
         <v>50</v>
       </c>
+      <c r="I250" s="2" t="s">
+        <v>2092</v>
+      </c>
       <c r="J250" t="s">
         <v>15</v>
       </c>
@@ -14857,7 +16595,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>1031</v>
       </c>
@@ -14882,6 +16620,9 @@
       <c r="H251" t="s">
         <v>461</v>
       </c>
+      <c r="I251" s="2" t="s">
+        <v>2093</v>
+      </c>
       <c r="J251" t="s">
         <v>15</v>
       </c>
@@ -14889,7 +16630,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>1035</v>
       </c>
@@ -14914,6 +16655,9 @@
       <c r="H252" t="s">
         <v>384</v>
       </c>
+      <c r="I252" s="2" t="s">
+        <v>2094</v>
+      </c>
       <c r="J252" t="s">
         <v>15</v>
       </c>
@@ -14921,7 +16665,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>1038</v>
       </c>
@@ -14946,6 +16690,9 @@
       <c r="H253" t="s">
         <v>1041</v>
       </c>
+      <c r="I253" s="2" t="s">
+        <v>2095</v>
+      </c>
       <c r="J253" t="s">
         <v>15</v>
       </c>
@@ -14953,7 +16700,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>1042</v>
       </c>
@@ -14978,6 +16725,9 @@
       <c r="H254" t="s">
         <v>1046</v>
       </c>
+      <c r="I254" s="2" t="s">
+        <v>2096</v>
+      </c>
       <c r="J254" t="s">
         <v>15</v>
       </c>
@@ -14985,7 +16735,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>1047</v>
       </c>
@@ -15010,6 +16760,9 @@
       <c r="H255" t="s">
         <v>1050</v>
       </c>
+      <c r="I255" s="2" t="s">
+        <v>2097</v>
+      </c>
       <c r="J255" t="s">
         <v>15</v>
       </c>
@@ -15017,7 +16770,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>1051</v>
       </c>
@@ -15042,6 +16795,9 @@
       <c r="H256" t="s">
         <v>1054</v>
       </c>
+      <c r="I256" s="2" t="s">
+        <v>2098</v>
+      </c>
       <c r="J256" t="s">
         <v>15</v>
       </c>
@@ -15049,7 +16805,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>1055</v>
       </c>
@@ -15074,6 +16830,9 @@
       <c r="H257" t="s">
         <v>1058</v>
       </c>
+      <c r="I257" s="2" t="s">
+        <v>2099</v>
+      </c>
       <c r="J257" t="s">
         <v>15</v>
       </c>
@@ -15081,7 +16840,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>1059</v>
       </c>
@@ -15106,6 +16865,9 @@
       <c r="H258" t="s">
         <v>216</v>
       </c>
+      <c r="I258" s="2" t="s">
+        <v>2100</v>
+      </c>
       <c r="J258" t="s">
         <v>15</v>
       </c>
@@ -15113,7 +16875,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>1060</v>
       </c>
@@ -15138,6 +16900,9 @@
       <c r="H259" t="s">
         <v>782</v>
       </c>
+      <c r="I259" s="2" t="s">
+        <v>2101</v>
+      </c>
       <c r="J259" t="s">
         <v>15</v>
       </c>
@@ -15145,7 +16910,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>1063</v>
       </c>
@@ -15170,6 +16935,9 @@
       <c r="H260" t="s">
         <v>332</v>
       </c>
+      <c r="I260" s="2" t="s">
+        <v>2102</v>
+      </c>
       <c r="J260" t="s">
         <v>15</v>
       </c>
@@ -15177,7 +16945,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>1067</v>
       </c>
@@ -15202,6 +16970,9 @@
       <c r="H261" t="s">
         <v>461</v>
       </c>
+      <c r="I261" s="2" t="s">
+        <v>2103</v>
+      </c>
       <c r="J261" t="s">
         <v>15</v>
       </c>
@@ -15209,7 +16980,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>1071</v>
       </c>
@@ -15234,6 +17005,9 @@
       <c r="H262" t="s">
         <v>139</v>
       </c>
+      <c r="I262" s="2" t="s">
+        <v>2104</v>
+      </c>
       <c r="J262" t="s">
         <v>15</v>
       </c>
@@ -15241,7 +17015,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1074</v>
       </c>
@@ -15266,6 +17040,9 @@
       <c r="H263" t="s">
         <v>1077</v>
       </c>
+      <c r="I263" s="2" t="s">
+        <v>2105</v>
+      </c>
       <c r="J263" t="s">
         <v>15</v>
       </c>
@@ -15273,7 +17050,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>1078</v>
       </c>
@@ -15298,6 +17075,9 @@
       <c r="H264" t="s">
         <v>1081</v>
       </c>
+      <c r="I264" s="2" t="s">
+        <v>2106</v>
+      </c>
       <c r="J264" t="s">
         <v>15</v>
       </c>
@@ -15305,7 +17085,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>1082</v>
       </c>
@@ -15330,6 +17110,9 @@
       <c r="H265" t="s">
         <v>36</v>
       </c>
+      <c r="I265" s="2" t="s">
+        <v>2107</v>
+      </c>
       <c r="J265" t="s">
         <v>15</v>
       </c>
@@ -15337,7 +17120,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>1086</v>
       </c>
@@ -15362,6 +17145,9 @@
       <c r="H266" t="s">
         <v>520</v>
       </c>
+      <c r="I266" s="2" t="s">
+        <v>2108</v>
+      </c>
       <c r="J266" t="s">
         <v>15</v>
       </c>
@@ -15369,7 +17155,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>1090</v>
       </c>
@@ -15394,6 +17180,9 @@
       <c r="H267" t="s">
         <v>303</v>
       </c>
+      <c r="I267" s="2" t="s">
+        <v>2109</v>
+      </c>
       <c r="J267" t="s">
         <v>15</v>
       </c>
@@ -15401,7 +17190,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>1093</v>
       </c>
@@ -15426,6 +17215,9 @@
       <c r="H268" t="s">
         <v>1097</v>
       </c>
+      <c r="I268" s="2" t="s">
+        <v>2110</v>
+      </c>
       <c r="J268" t="s">
         <v>15</v>
       </c>
@@ -15433,7 +17225,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>1098</v>
       </c>
@@ -15458,6 +17250,9 @@
       <c r="H269" t="s">
         <v>1101</v>
       </c>
+      <c r="I269" s="2" t="s">
+        <v>2111</v>
+      </c>
       <c r="J269" t="s">
         <v>15</v>
       </c>
@@ -15465,7 +17260,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>1102</v>
       </c>
@@ -15490,6 +17285,9 @@
       <c r="H270" t="s">
         <v>1105</v>
       </c>
+      <c r="I270" s="2" t="s">
+        <v>2112</v>
+      </c>
       <c r="J270" t="s">
         <v>15</v>
       </c>
@@ -15497,7 +17295,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>1106</v>
       </c>
@@ -15522,6 +17320,9 @@
       <c r="H271" t="s">
         <v>1027</v>
       </c>
+      <c r="I271" s="2" t="s">
+        <v>2113</v>
+      </c>
       <c r="J271" t="s">
         <v>15</v>
       </c>
@@ -15529,7 +17330,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>1110</v>
       </c>
@@ -15554,6 +17355,9 @@
       <c r="H272" t="s">
         <v>1113</v>
       </c>
+      <c r="I272" s="2" t="s">
+        <v>2114</v>
+      </c>
       <c r="J272" t="s">
         <v>15</v>
       </c>
@@ -15561,7 +17365,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>1114</v>
       </c>
@@ -15586,6 +17390,9 @@
       <c r="H273" t="s">
         <v>1117</v>
       </c>
+      <c r="I273" s="2" t="s">
+        <v>2115</v>
+      </c>
       <c r="J273" t="s">
         <v>15</v>
       </c>
@@ -15593,7 +17400,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>1118</v>
       </c>
@@ -15618,6 +17425,9 @@
       <c r="H274" t="s">
         <v>844</v>
       </c>
+      <c r="I274" s="2" t="s">
+        <v>2116</v>
+      </c>
       <c r="J274" t="s">
         <v>15</v>
       </c>
@@ -15625,7 +17435,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>1121</v>
       </c>
@@ -15650,6 +17460,9 @@
       <c r="H275" t="s">
         <v>1125</v>
       </c>
+      <c r="I275" s="2" t="s">
+        <v>2117</v>
+      </c>
       <c r="J275" t="s">
         <v>15</v>
       </c>
@@ -15657,7 +17470,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1126</v>
       </c>
@@ -15682,6 +17495,9 @@
       <c r="H276" t="s">
         <v>1130</v>
       </c>
+      <c r="I276" s="2" t="s">
+        <v>2118</v>
+      </c>
       <c r="J276" t="s">
         <v>15</v>
       </c>
@@ -15689,7 +17505,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1131</v>
       </c>
@@ -15714,6 +17530,9 @@
       <c r="H277" t="s">
         <v>1134</v>
       </c>
+      <c r="I277" s="2" t="s">
+        <v>2119</v>
+      </c>
       <c r="J277" t="s">
         <v>1944</v>
       </c>
@@ -15721,7 +17540,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>1135</v>
       </c>
@@ -15746,6 +17565,9 @@
       <c r="H278" t="s">
         <v>1081</v>
       </c>
+      <c r="I278" s="2" t="s">
+        <v>2120</v>
+      </c>
       <c r="J278" t="s">
         <v>15</v>
       </c>
@@ -15753,7 +17575,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1138</v>
       </c>
@@ -15778,6 +17600,9 @@
       <c r="H279" t="s">
         <v>448</v>
       </c>
+      <c r="I279" s="2" t="s">
+        <v>2121</v>
+      </c>
       <c r="J279" t="s">
         <v>15</v>
       </c>
@@ -15785,7 +17610,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>1142</v>
       </c>
@@ -15810,6 +17635,9 @@
       <c r="H280" t="s">
         <v>635</v>
       </c>
+      <c r="I280" s="2" t="s">
+        <v>2122</v>
+      </c>
       <c r="J280" t="s">
         <v>15</v>
       </c>
@@ -15817,7 +17645,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>1145</v>
       </c>
@@ -15842,6 +17670,9 @@
       <c r="H281" t="s">
         <v>115</v>
       </c>
+      <c r="I281" s="2" t="s">
+        <v>2123</v>
+      </c>
       <c r="J281" t="s">
         <v>15</v>
       </c>
@@ -15849,7 +17680,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>1148</v>
       </c>
@@ -15874,6 +17705,9 @@
       <c r="H282" t="s">
         <v>73</v>
       </c>
+      <c r="I282" s="2" t="s">
+        <v>2124</v>
+      </c>
       <c r="J282" t="s">
         <v>15</v>
       </c>
@@ -15881,7 +17715,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>1151</v>
       </c>
@@ -15906,6 +17740,9 @@
       <c r="H283" t="s">
         <v>1154</v>
       </c>
+      <c r="I283" s="2" t="s">
+        <v>2125</v>
+      </c>
       <c r="J283" t="s">
         <v>15</v>
       </c>
@@ -15913,7 +17750,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1155</v>
       </c>
@@ -15938,6 +17775,9 @@
       <c r="H284" t="s">
         <v>1158</v>
       </c>
+      <c r="I284" s="2" t="s">
+        <v>2126</v>
+      </c>
       <c r="J284" t="s">
         <v>15</v>
       </c>
@@ -15945,7 +17785,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1159</v>
       </c>
@@ -15970,6 +17810,9 @@
       <c r="H285" t="s">
         <v>1162</v>
       </c>
+      <c r="I285" s="2" t="s">
+        <v>2127</v>
+      </c>
       <c r="J285" t="s">
         <v>15</v>
       </c>
@@ -15977,7 +17820,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1163</v>
       </c>
@@ -16002,6 +17845,9 @@
       <c r="H286" t="s">
         <v>1166</v>
       </c>
+      <c r="I286" s="2" t="s">
+        <v>2128</v>
+      </c>
       <c r="J286" t="s">
         <v>15</v>
       </c>
@@ -16009,7 +17855,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>1167</v>
       </c>
@@ -16034,6 +17880,9 @@
       <c r="H287" t="s">
         <v>216</v>
       </c>
+      <c r="I287" s="2" t="s">
+        <v>2129</v>
+      </c>
       <c r="J287" t="s">
         <v>15</v>
       </c>
@@ -16041,7 +17890,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>1171</v>
       </c>
@@ -16066,6 +17915,9 @@
       <c r="H288" t="s">
         <v>1175</v>
       </c>
+      <c r="I288" s="2" t="s">
+        <v>2130</v>
+      </c>
       <c r="J288" t="s">
         <v>15</v>
       </c>
@@ -16073,7 +17925,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>1176</v>
       </c>
@@ -16098,6 +17950,9 @@
       <c r="H289" t="s">
         <v>1180</v>
       </c>
+      <c r="I289" s="2" t="s">
+        <v>2131</v>
+      </c>
       <c r="J289" t="s">
         <v>15</v>
       </c>
@@ -16105,7 +17960,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>1181</v>
       </c>
@@ -16130,6 +17985,9 @@
       <c r="H290" t="s">
         <v>1184</v>
       </c>
+      <c r="I290" s="2" t="s">
+        <v>2132</v>
+      </c>
       <c r="J290" t="s">
         <v>15</v>
       </c>
@@ -16137,7 +17995,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>1185</v>
       </c>
@@ -16162,6 +18020,9 @@
       <c r="H291" t="s">
         <v>1188</v>
       </c>
+      <c r="I291" s="2" t="s">
+        <v>2133</v>
+      </c>
       <c r="J291" t="s">
         <v>15</v>
       </c>
@@ -16169,7 +18030,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>1189</v>
       </c>
@@ -16194,6 +18055,9 @@
       <c r="H292" t="s">
         <v>180</v>
       </c>
+      <c r="I292" s="2" t="s">
+        <v>2134</v>
+      </c>
       <c r="J292" t="s">
         <v>15</v>
       </c>
@@ -16201,7 +18065,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>1192</v>
       </c>
@@ -16226,6 +18090,9 @@
       <c r="H293" t="s">
         <v>1196</v>
       </c>
+      <c r="I293" s="2" t="s">
+        <v>2135</v>
+      </c>
       <c r="J293" t="s">
         <v>15</v>
       </c>
@@ -16233,7 +18100,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>1197</v>
       </c>
@@ -16258,6 +18125,9 @@
       <c r="H294" t="s">
         <v>1200</v>
       </c>
+      <c r="I294" s="2" t="s">
+        <v>2136</v>
+      </c>
       <c r="J294" t="s">
         <v>15</v>
       </c>
@@ -16265,7 +18135,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>1201</v>
       </c>
@@ -16290,6 +18160,9 @@
       <c r="H295" t="s">
         <v>1204</v>
       </c>
+      <c r="I295" s="2" t="s">
+        <v>2137</v>
+      </c>
       <c r="J295" t="s">
         <v>15</v>
       </c>
@@ -16297,7 +18170,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>1205</v>
       </c>
@@ -16322,6 +18195,9 @@
       <c r="H296" t="s">
         <v>1208</v>
       </c>
+      <c r="I296" s="2" t="s">
+        <v>2138</v>
+      </c>
       <c r="J296" t="s">
         <v>15</v>
       </c>
@@ -16329,7 +18205,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>1209</v>
       </c>
@@ -16354,6 +18230,9 @@
       <c r="H297" t="s">
         <v>812</v>
       </c>
+      <c r="I297" s="2" t="s">
+        <v>2139</v>
+      </c>
       <c r="J297" t="s">
         <v>15</v>
       </c>
@@ -16361,7 +18240,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>1213</v>
       </c>
@@ -16386,6 +18265,9 @@
       <c r="H298" t="s">
         <v>1097</v>
       </c>
+      <c r="I298" s="2" t="s">
+        <v>2140</v>
+      </c>
       <c r="J298" t="s">
         <v>15</v>
       </c>
@@ -16393,7 +18275,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>1217</v>
       </c>
@@ -16418,6 +18300,9 @@
       <c r="H299" t="s">
         <v>191</v>
       </c>
+      <c r="I299" s="2" t="s">
+        <v>2141</v>
+      </c>
       <c r="J299" t="s">
         <v>15</v>
       </c>
@@ -16425,7 +18310,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>1220</v>
       </c>
@@ -16450,6 +18335,9 @@
       <c r="H300" t="s">
         <v>110</v>
       </c>
+      <c r="I300" s="2" t="s">
+        <v>2142</v>
+      </c>
       <c r="J300" t="s">
         <v>15</v>
       </c>
@@ -16457,7 +18345,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>1223</v>
       </c>
@@ -16482,6 +18370,9 @@
       <c r="H301" t="s">
         <v>1226</v>
       </c>
+      <c r="I301" t="s">
+        <v>2143</v>
+      </c>
       <c r="J301" t="s">
         <v>15</v>
       </c>
@@ -16489,7 +18380,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>1227</v>
       </c>
@@ -16514,6 +18405,9 @@
       <c r="H302" t="s">
         <v>1231</v>
       </c>
+      <c r="I302" t="s">
+        <v>2144</v>
+      </c>
       <c r="J302" t="s">
         <v>15</v>
       </c>
@@ -16521,7 +18415,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>1232</v>
       </c>
@@ -16546,6 +18440,9 @@
       <c r="H303" t="s">
         <v>1235</v>
       </c>
+      <c r="I303" t="s">
+        <v>2145</v>
+      </c>
       <c r="J303" t="s">
         <v>15</v>
       </c>
@@ -16553,7 +18450,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>1236</v>
       </c>
@@ -16578,6 +18475,9 @@
       <c r="H304" t="s">
         <v>403</v>
       </c>
+      <c r="I304" t="s">
+        <v>2146</v>
+      </c>
       <c r="J304" t="s">
         <v>15</v>
       </c>
@@ -16585,7 +18485,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>1239</v>
       </c>
@@ -16610,6 +18510,9 @@
       <c r="H305" t="s">
         <v>476</v>
       </c>
+      <c r="I305" t="s">
+        <v>2147</v>
+      </c>
       <c r="J305" t="s">
         <v>15</v>
       </c>
@@ -16617,7 +18520,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>1242</v>
       </c>
@@ -16642,6 +18545,9 @@
       <c r="H306" t="s">
         <v>934</v>
       </c>
+      <c r="I306" s="2" t="s">
+        <v>2148</v>
+      </c>
       <c r="J306" t="s">
         <v>15</v>
       </c>
@@ -16649,7 +18555,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>1245</v>
       </c>
@@ -16674,6 +18580,9 @@
       <c r="H307" t="s">
         <v>801</v>
       </c>
+      <c r="I307" t="s">
+        <v>2149</v>
+      </c>
       <c r="J307" t="s">
         <v>15</v>
       </c>
@@ -16681,7 +18590,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>1248</v>
       </c>
@@ -16706,6 +18615,9 @@
       <c r="H308" t="s">
         <v>115</v>
       </c>
+      <c r="I308" t="s">
+        <v>2150</v>
+      </c>
       <c r="J308" t="s">
         <v>15</v>
       </c>
@@ -16713,7 +18625,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>1251</v>
       </c>
@@ -16738,6 +18650,9 @@
       <c r="H309" t="s">
         <v>139</v>
       </c>
+      <c r="I309" t="s">
+        <v>2151</v>
+      </c>
       <c r="J309" t="s">
         <v>15</v>
       </c>
@@ -16745,7 +18660,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>1254</v>
       </c>
@@ -16770,6 +18685,9 @@
       <c r="H310" t="s">
         <v>977</v>
       </c>
+      <c r="I310" t="s">
+        <v>2152</v>
+      </c>
       <c r="J310" t="s">
         <v>15</v>
       </c>
@@ -16777,7 +18695,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>1257</v>
       </c>
@@ -16802,6 +18720,9 @@
       <c r="H311" t="s">
         <v>36</v>
       </c>
+      <c r="I311" t="s">
+        <v>2153</v>
+      </c>
       <c r="J311" t="s">
         <v>15</v>
       </c>
@@ -16809,7 +18730,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>1260</v>
       </c>
@@ -16834,6 +18755,9 @@
       <c r="H312" t="s">
         <v>1263</v>
       </c>
+      <c r="I312" t="s">
+        <v>2154</v>
+      </c>
       <c r="J312" t="s">
         <v>15</v>
       </c>
@@ -16841,7 +18765,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>1264</v>
       </c>
@@ -16866,6 +18790,9 @@
       <c r="H313" t="s">
         <v>476</v>
       </c>
+      <c r="I313" t="s">
+        <v>2155</v>
+      </c>
       <c r="J313" t="s">
         <v>15</v>
       </c>
@@ -16873,7 +18800,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>1267</v>
       </c>
@@ -16898,6 +18825,9 @@
       <c r="H314" t="s">
         <v>661</v>
       </c>
+      <c r="I314" t="s">
+        <v>2156</v>
+      </c>
       <c r="J314" t="s">
         <v>15</v>
       </c>
@@ -16905,7 +18835,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>1270</v>
       </c>
@@ -16930,6 +18860,9 @@
       <c r="H315" t="s">
         <v>73</v>
       </c>
+      <c r="I315" t="s">
+        <v>2157</v>
+      </c>
       <c r="J315" t="s">
         <v>15</v>
       </c>
@@ -16937,7 +18870,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>1274</v>
       </c>
@@ -16962,6 +18895,9 @@
       <c r="H316" t="s">
         <v>1277</v>
       </c>
+      <c r="I316" t="s">
+        <v>2158</v>
+      </c>
       <c r="J316" t="s">
         <v>15</v>
       </c>
@@ -16969,7 +18905,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>1278</v>
       </c>
@@ -16994,6 +18930,9 @@
       <c r="H317" t="s">
         <v>604</v>
       </c>
+      <c r="I317" t="s">
+        <v>2159</v>
+      </c>
       <c r="J317" t="s">
         <v>15</v>
       </c>
@@ -17001,7 +18940,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>1282</v>
       </c>
@@ -17026,6 +18965,9 @@
       <c r="H318" t="s">
         <v>1285</v>
       </c>
+      <c r="I318" t="s">
+        <v>2160</v>
+      </c>
       <c r="J318" t="s">
         <v>15</v>
       </c>
@@ -17033,7 +18975,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>1286</v>
       </c>
@@ -17058,6 +19000,9 @@
       <c r="H319" t="s">
         <v>1289</v>
       </c>
+      <c r="I319" t="s">
+        <v>2161</v>
+      </c>
       <c r="J319" t="s">
         <v>15</v>
       </c>
@@ -17065,7 +19010,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>1290</v>
       </c>
@@ -17090,6 +19035,9 @@
       <c r="H320" t="s">
         <v>1294</v>
       </c>
+      <c r="I320" t="s">
+        <v>2162</v>
+      </c>
       <c r="J320" t="s">
         <v>15</v>
       </c>
@@ -17097,7 +19045,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>1295</v>
       </c>
@@ -17122,6 +19070,9 @@
       <c r="H321" t="s">
         <v>490</v>
       </c>
+      <c r="I321" t="s">
+        <v>2163</v>
+      </c>
       <c r="J321" t="s">
         <v>15</v>
       </c>
@@ -17129,7 +19080,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>1298</v>
       </c>
@@ -17154,6 +19105,9 @@
       <c r="H322" t="s">
         <v>1302</v>
       </c>
+      <c r="I322" t="s">
+        <v>2164</v>
+      </c>
       <c r="J322" t="s">
         <v>15</v>
       </c>
@@ -17161,7 +19115,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>1303</v>
       </c>
@@ -17186,6 +19140,9 @@
       <c r="H323" t="s">
         <v>1307</v>
       </c>
+      <c r="I323" t="s">
+        <v>2165</v>
+      </c>
       <c r="J323" t="s">
         <v>15</v>
       </c>
@@ -17193,7 +19150,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>1308</v>
       </c>
@@ -17218,6 +19175,9 @@
       <c r="H324" t="s">
         <v>665</v>
       </c>
+      <c r="I324" t="s">
+        <v>2166</v>
+      </c>
       <c r="J324" t="s">
         <v>15</v>
       </c>
@@ -17225,7 +19185,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>1311</v>
       </c>
@@ -17250,6 +19210,9 @@
       <c r="H325" t="s">
         <v>308</v>
       </c>
+      <c r="I325" t="s">
+        <v>2167</v>
+      </c>
       <c r="J325" t="s">
         <v>15</v>
       </c>
@@ -17257,7 +19220,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>1314</v>
       </c>
@@ -17282,6 +19245,9 @@
       <c r="H326" t="s">
         <v>812</v>
       </c>
+      <c r="I326" t="s">
+        <v>2168</v>
+      </c>
       <c r="J326" t="s">
         <v>15</v>
       </c>
@@ -17289,7 +19255,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>1317</v>
       </c>
@@ -17314,6 +19280,9 @@
       <c r="H327" t="s">
         <v>69</v>
       </c>
+      <c r="I327" t="s">
+        <v>2169</v>
+      </c>
       <c r="J327" t="s">
         <v>15</v>
       </c>
@@ -17321,7 +19290,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>1320</v>
       </c>
@@ -17346,6 +19315,9 @@
       <c r="H328" t="s">
         <v>1323</v>
       </c>
+      <c r="I328" t="s">
+        <v>2170</v>
+      </c>
       <c r="J328" t="s">
         <v>15</v>
       </c>
@@ -17353,7 +19325,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>1324</v>
       </c>
@@ -17378,6 +19350,9 @@
       <c r="H329" t="s">
         <v>1158</v>
       </c>
+      <c r="I329" t="s">
+        <v>2171</v>
+      </c>
       <c r="J329" t="s">
         <v>15</v>
       </c>
@@ -17385,7 +19360,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>1328</v>
       </c>
@@ -17410,6 +19385,9 @@
       <c r="H330" t="s">
         <v>1331</v>
       </c>
+      <c r="I330" t="s">
+        <v>2418</v>
+      </c>
       <c r="J330" t="s">
         <v>15</v>
       </c>
@@ -17417,7 +19395,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>1332</v>
       </c>
@@ -17442,6 +19420,9 @@
       <c r="H331" t="s">
         <v>1335</v>
       </c>
+      <c r="I331" t="s">
+        <v>2172</v>
+      </c>
       <c r="J331" t="s">
         <v>15</v>
       </c>
@@ -17449,7 +19430,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>1336</v>
       </c>
@@ -17474,6 +19455,9 @@
       <c r="H332" t="s">
         <v>555</v>
       </c>
+      <c r="I332" s="2" t="s">
+        <v>2173</v>
+      </c>
       <c r="J332" t="s">
         <v>15</v>
       </c>
@@ -17481,7 +19465,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>1339</v>
       </c>
@@ -17506,6 +19490,9 @@
       <c r="H333" t="s">
         <v>654</v>
       </c>
+      <c r="I333" t="s">
+        <v>2174</v>
+      </c>
       <c r="J333" t="s">
         <v>15</v>
       </c>
@@ -17513,7 +19500,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>1342</v>
       </c>
@@ -17538,6 +19525,9 @@
       <c r="H334" t="s">
         <v>332</v>
       </c>
+      <c r="I334" t="s">
+        <v>2175</v>
+      </c>
       <c r="J334" t="s">
         <v>15</v>
       </c>
@@ -17545,7 +19535,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>1345</v>
       </c>
@@ -17570,7 +19560,9 @@
       <c r="H335" t="s">
         <v>1348</v>
       </c>
-      <c r="I335" s="2"/>
+      <c r="I335" t="s">
+        <v>2176</v>
+      </c>
       <c r="J335" t="s">
         <v>15</v>
       </c>
@@ -17578,7 +19570,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>1349</v>
       </c>
@@ -17603,6 +19595,9 @@
       <c r="H336" t="s">
         <v>520</v>
       </c>
+      <c r="I336" t="s">
+        <v>2177</v>
+      </c>
       <c r="J336" t="s">
         <v>15</v>
       </c>
@@ -17610,7 +19605,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>1353</v>
       </c>
@@ -17635,6 +19630,9 @@
       <c r="H337" t="s">
         <v>1356</v>
       </c>
+      <c r="I337" t="s">
+        <v>2178</v>
+      </c>
       <c r="J337" t="s">
         <v>15</v>
       </c>
@@ -17642,7 +19640,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>1357</v>
       </c>
@@ -17667,6 +19665,9 @@
       <c r="H338" t="s">
         <v>290</v>
       </c>
+      <c r="I338" t="s">
+        <v>2179</v>
+      </c>
       <c r="J338" t="s">
         <v>15</v>
       </c>
@@ -17674,7 +19675,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>1361</v>
       </c>
@@ -17699,6 +19700,9 @@
       <c r="H339" t="s">
         <v>654</v>
       </c>
+      <c r="I339" t="s">
+        <v>2180</v>
+      </c>
       <c r="J339" t="s">
         <v>15</v>
       </c>
@@ -17706,7 +19710,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>1365</v>
       </c>
@@ -17731,6 +19735,9 @@
       <c r="H340" t="s">
         <v>1180</v>
       </c>
+      <c r="I340" t="s">
+        <v>2181</v>
+      </c>
       <c r="J340" t="s">
         <v>15</v>
       </c>
@@ -17738,7 +19745,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>1368</v>
       </c>
@@ -17763,6 +19770,9 @@
       <c r="H341" t="s">
         <v>172</v>
       </c>
+      <c r="I341" t="s">
+        <v>2182</v>
+      </c>
       <c r="J341" t="s">
         <v>15</v>
       </c>
@@ -17770,7 +19780,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>1371</v>
       </c>
@@ -17795,6 +19805,9 @@
       <c r="H342" t="s">
         <v>1374</v>
       </c>
+      <c r="I342" t="s">
+        <v>2183</v>
+      </c>
       <c r="J342" t="s">
         <v>15</v>
       </c>
@@ -17802,7 +19815,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>1375</v>
       </c>
@@ -17827,6 +19840,9 @@
       <c r="H343" t="s">
         <v>1378</v>
       </c>
+      <c r="I343" t="s">
+        <v>2419</v>
+      </c>
       <c r="J343" t="s">
         <v>15</v>
       </c>
@@ -17834,7 +19850,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>1379</v>
       </c>
@@ -17859,7 +19875,9 @@
       <c r="H344" t="s">
         <v>1383</v>
       </c>
-      <c r="I344" s="2"/>
+      <c r="I344" t="s">
+        <v>2184</v>
+      </c>
       <c r="J344" t="s">
         <v>15</v>
       </c>
@@ -17867,7 +19885,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>1384</v>
       </c>
@@ -17892,6 +19910,9 @@
       <c r="H345" t="s">
         <v>1387</v>
       </c>
+      <c r="I345" t="s">
+        <v>2185</v>
+      </c>
       <c r="J345" t="s">
         <v>15</v>
       </c>
@@ -17899,7 +19920,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>1388</v>
       </c>
@@ -17924,6 +19945,9 @@
       <c r="H346" t="s">
         <v>529</v>
       </c>
+      <c r="I346" t="s">
+        <v>2186</v>
+      </c>
       <c r="J346" t="s">
         <v>15</v>
       </c>
@@ -17931,7 +19955,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>1392</v>
       </c>
@@ -17956,6 +19980,9 @@
       <c r="H347" t="s">
         <v>1395</v>
       </c>
+      <c r="I347" t="s">
+        <v>2187</v>
+      </c>
       <c r="J347" t="s">
         <v>15</v>
       </c>
@@ -17963,7 +19990,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>1396</v>
       </c>
@@ -17988,6 +20015,9 @@
       <c r="H348" t="s">
         <v>639</v>
       </c>
+      <c r="I348" t="s">
+        <v>2188</v>
+      </c>
       <c r="J348" t="s">
         <v>15</v>
       </c>
@@ -17995,7 +20025,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>1400</v>
       </c>
@@ -18020,6 +20050,9 @@
       <c r="H349" t="s">
         <v>294</v>
       </c>
+      <c r="I349" t="s">
+        <v>2189</v>
+      </c>
       <c r="J349" t="s">
         <v>15</v>
       </c>
@@ -18027,7 +20060,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>1403</v>
       </c>
@@ -18052,6 +20085,9 @@
       <c r="H350" t="s">
         <v>229</v>
       </c>
+      <c r="I350" t="s">
+        <v>2190</v>
+      </c>
       <c r="J350" t="s">
         <v>15</v>
       </c>
@@ -18059,7 +20095,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>1406</v>
       </c>
@@ -18084,6 +20120,9 @@
       <c r="H351" t="s">
         <v>1409</v>
       </c>
+      <c r="I351" t="s">
+        <v>2191</v>
+      </c>
       <c r="J351" t="s">
         <v>15</v>
       </c>
@@ -18091,7 +20130,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>1410</v>
       </c>
@@ -18116,6 +20155,9 @@
       <c r="H352" t="s">
         <v>1413</v>
       </c>
+      <c r="I352" t="s">
+        <v>2192</v>
+      </c>
       <c r="J352" t="s">
         <v>15</v>
       </c>
@@ -18123,7 +20165,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>1414</v>
       </c>
@@ -18148,6 +20190,9 @@
       <c r="H353" t="s">
         <v>1188</v>
       </c>
+      <c r="I353" t="s">
+        <v>2434</v>
+      </c>
       <c r="J353" t="s">
         <v>15</v>
       </c>
@@ -18155,7 +20200,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>1418</v>
       </c>
@@ -18180,6 +20225,9 @@
       <c r="H354" t="s">
         <v>1421</v>
       </c>
+      <c r="I354" t="s">
+        <v>2193</v>
+      </c>
       <c r="J354" t="s">
         <v>15</v>
       </c>
@@ -18187,7 +20235,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>1422</v>
       </c>
@@ -18212,6 +20260,9 @@
       <c r="H355" t="s">
         <v>977</v>
       </c>
+      <c r="I355" t="s">
+        <v>2194</v>
+      </c>
       <c r="J355" t="s">
         <v>15</v>
       </c>
@@ -18219,7 +20270,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>1426</v>
       </c>
@@ -18244,6 +20295,9 @@
       <c r="H356" t="s">
         <v>1430</v>
       </c>
+      <c r="I356" t="s">
+        <v>2420</v>
+      </c>
       <c r="J356" t="s">
         <v>15</v>
       </c>
@@ -18251,7 +20305,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>1431</v>
       </c>
@@ -18276,6 +20330,9 @@
       <c r="H357" t="s">
         <v>50</v>
       </c>
+      <c r="I357" t="s">
+        <v>2195</v>
+      </c>
       <c r="J357" t="s">
         <v>15</v>
       </c>
@@ -18283,7 +20340,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>1435</v>
       </c>
@@ -18308,6 +20365,9 @@
       <c r="H358" t="s">
         <v>1438</v>
       </c>
+      <c r="I358" t="s">
+        <v>2421</v>
+      </c>
       <c r="J358" t="s">
         <v>15</v>
       </c>
@@ -18315,7 +20375,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>1439</v>
       </c>
@@ -18340,6 +20400,9 @@
       <c r="H359" t="s">
         <v>1443</v>
       </c>
+      <c r="I359" t="s">
+        <v>2196</v>
+      </c>
       <c r="J359" t="s">
         <v>15</v>
       </c>
@@ -18347,7 +20410,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>1444</v>
       </c>
@@ -18372,6 +20435,9 @@
       <c r="H360" t="s">
         <v>1448</v>
       </c>
+      <c r="I360" t="s">
+        <v>2197</v>
+      </c>
       <c r="J360" t="s">
         <v>15</v>
       </c>
@@ -18379,7 +20445,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>1449</v>
       </c>
@@ -18404,7 +20470,9 @@
       <c r="H361" t="s">
         <v>1452</v>
       </c>
-      <c r="I361" s="2"/>
+      <c r="I361" t="s">
+        <v>2422</v>
+      </c>
       <c r="J361" t="s">
         <v>15</v>
       </c>
@@ -18412,7 +20480,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>1453</v>
       </c>
@@ -18437,6 +20505,9 @@
       <c r="H362" t="s">
         <v>1457</v>
       </c>
+      <c r="I362" t="s">
+        <v>2198</v>
+      </c>
       <c r="J362" t="s">
         <v>15</v>
       </c>
@@ -18444,7 +20515,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>1458</v>
       </c>
@@ -18469,6 +20540,9 @@
       <c r="H363" t="s">
         <v>1461</v>
       </c>
+      <c r="I363" t="s">
+        <v>2199</v>
+      </c>
       <c r="J363" t="s">
         <v>15</v>
       </c>
@@ -18476,7 +20550,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>1462</v>
       </c>
@@ -18501,6 +20575,9 @@
       <c r="H364" t="s">
         <v>1058</v>
       </c>
+      <c r="I364" t="s">
+        <v>2200</v>
+      </c>
       <c r="J364" t="s">
         <v>15</v>
       </c>
@@ -18508,7 +20585,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>1465</v>
       </c>
@@ -18533,6 +20610,9 @@
       <c r="H365" t="s">
         <v>476</v>
       </c>
+      <c r="I365" t="s">
+        <v>2201</v>
+      </c>
       <c r="J365" t="s">
         <v>15</v>
       </c>
@@ -18540,7 +20620,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>1469</v>
       </c>
@@ -18565,6 +20645,9 @@
       <c r="H366" t="s">
         <v>1472</v>
       </c>
+      <c r="I366" t="s">
+        <v>2202</v>
+      </c>
       <c r="J366" t="s">
         <v>15</v>
       </c>
@@ -18572,7 +20655,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>1473</v>
       </c>
@@ -18597,6 +20680,9 @@
       <c r="H367" t="s">
         <v>1438</v>
       </c>
+      <c r="I367" t="s">
+        <v>2203</v>
+      </c>
       <c r="J367" t="s">
         <v>15</v>
       </c>
@@ -18604,7 +20690,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>1476</v>
       </c>
@@ -18629,6 +20715,9 @@
       <c r="H368" t="s">
         <v>1479</v>
       </c>
+      <c r="I368" t="s">
+        <v>2204</v>
+      </c>
       <c r="J368" t="s">
         <v>15</v>
       </c>
@@ -18636,7 +20725,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>1480</v>
       </c>
@@ -18661,6 +20750,9 @@
       <c r="H369" t="s">
         <v>1483</v>
       </c>
+      <c r="I369" t="s">
+        <v>2205</v>
+      </c>
       <c r="J369" t="s">
         <v>15</v>
       </c>
@@ -18668,7 +20760,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>1484</v>
       </c>
@@ -18693,6 +20785,9 @@
       <c r="H370" t="s">
         <v>1487</v>
       </c>
+      <c r="I370" t="s">
+        <v>2206</v>
+      </c>
       <c r="J370" t="s">
         <v>15</v>
       </c>
@@ -18700,7 +20795,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>1488</v>
       </c>
@@ -18725,6 +20820,9 @@
       <c r="H371" t="s">
         <v>1204</v>
       </c>
+      <c r="I371" t="s">
+        <v>2207</v>
+      </c>
       <c r="J371" t="s">
         <v>15</v>
       </c>
@@ -18732,7 +20830,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>1491</v>
       </c>
@@ -18757,6 +20855,9 @@
       <c r="H372" t="s">
         <v>162</v>
       </c>
+      <c r="I372" t="s">
+        <v>2423</v>
+      </c>
       <c r="J372" t="s">
         <v>15</v>
       </c>
@@ -18764,7 +20865,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>1494</v>
       </c>
@@ -18789,6 +20890,9 @@
       <c r="H373" t="s">
         <v>1497</v>
       </c>
+      <c r="I373" t="s">
+        <v>2208</v>
+      </c>
       <c r="J373" t="s">
         <v>15</v>
       </c>
@@ -18796,7 +20900,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>1498</v>
       </c>
@@ -18821,6 +20925,9 @@
       <c r="H374" t="s">
         <v>909</v>
       </c>
+      <c r="I374" t="s">
+        <v>2209</v>
+      </c>
       <c r="J374" t="s">
         <v>15</v>
       </c>
@@ -18828,7 +20935,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>1501</v>
       </c>
@@ -18853,6 +20960,9 @@
       <c r="H375" t="s">
         <v>55</v>
       </c>
+      <c r="I375" t="s">
+        <v>2210</v>
+      </c>
       <c r="J375" t="s">
         <v>15</v>
       </c>
@@ -18860,7 +20970,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>1504</v>
       </c>
@@ -18885,6 +20995,9 @@
       <c r="H376" t="s">
         <v>682</v>
       </c>
+      <c r="I376" t="s">
+        <v>2211</v>
+      </c>
       <c r="J376" t="s">
         <v>15</v>
       </c>
@@ -18892,7 +21005,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>1508</v>
       </c>
@@ -18917,6 +21030,9 @@
       <c r="H377" t="s">
         <v>1511</v>
       </c>
+      <c r="I377" t="s">
+        <v>2212</v>
+      </c>
       <c r="J377" t="s">
         <v>15</v>
       </c>
@@ -18924,7 +21040,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>1512</v>
       </c>
@@ -18949,6 +21065,9 @@
       <c r="H378" t="s">
         <v>1516</v>
       </c>
+      <c r="I378" t="s">
+        <v>2424</v>
+      </c>
       <c r="J378" t="s">
         <v>15</v>
       </c>
@@ -18956,7 +21075,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>1517</v>
       </c>
@@ -18981,6 +21100,9 @@
       <c r="H379" t="s">
         <v>255</v>
       </c>
+      <c r="I379" t="s">
+        <v>2213</v>
+      </c>
       <c r="J379" t="s">
         <v>15</v>
       </c>
@@ -18988,7 +21110,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>1520</v>
       </c>
@@ -19013,6 +21135,9 @@
       <c r="H380" t="s">
         <v>50</v>
       </c>
+      <c r="I380" t="s">
+        <v>2214</v>
+      </c>
       <c r="J380" t="s">
         <v>15</v>
       </c>
@@ -19020,7 +21145,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>1524</v>
       </c>
@@ -19045,6 +21170,9 @@
       <c r="H381" t="s">
         <v>1527</v>
       </c>
+      <c r="I381" t="s">
+        <v>2215</v>
+      </c>
       <c r="J381" t="s">
         <v>15</v>
       </c>
@@ -19052,7 +21180,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>1528</v>
       </c>
@@ -19077,6 +21205,9 @@
       <c r="H382" t="s">
         <v>1457</v>
       </c>
+      <c r="I382" t="s">
+        <v>2425</v>
+      </c>
       <c r="J382" t="s">
         <v>15</v>
       </c>
@@ -19084,7 +21215,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>1532</v>
       </c>
@@ -19109,6 +21240,9 @@
       <c r="H383" t="s">
         <v>490</v>
       </c>
+      <c r="I383" t="s">
+        <v>2163</v>
+      </c>
       <c r="J383" t="s">
         <v>15</v>
       </c>
@@ -19116,7 +21250,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>1535</v>
       </c>
@@ -19141,6 +21275,9 @@
       <c r="H384" t="s">
         <v>466</v>
       </c>
+      <c r="I384" t="s">
+        <v>2435</v>
+      </c>
       <c r="J384" t="s">
         <v>15</v>
       </c>
@@ -19148,7 +21285,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>1539</v>
       </c>
@@ -19173,6 +21310,9 @@
       <c r="H385" t="s">
         <v>73</v>
       </c>
+      <c r="I385" t="s">
+        <v>2216</v>
+      </c>
       <c r="J385" t="s">
         <v>15</v>
       </c>
@@ -19180,7 +21320,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>1543</v>
       </c>
@@ -19205,7 +21345,9 @@
       <c r="H386" t="s">
         <v>1546</v>
       </c>
-      <c r="I386" s="2"/>
+      <c r="I386" t="s">
+        <v>2217</v>
+      </c>
       <c r="J386" t="s">
         <v>15</v>
       </c>
@@ -19213,7 +21355,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>1547</v>
       </c>
@@ -19238,6 +21380,9 @@
       <c r="H387" t="s">
         <v>461</v>
       </c>
+      <c r="I387" t="s">
+        <v>2426</v>
+      </c>
       <c r="J387" t="s">
         <v>15</v>
       </c>
@@ -19245,7 +21390,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>1550</v>
       </c>
@@ -19270,6 +21415,9 @@
       <c r="H388" t="s">
         <v>332</v>
       </c>
+      <c r="I388" t="s">
+        <v>2218</v>
+      </c>
       <c r="J388" t="s">
         <v>15</v>
       </c>
@@ -19277,7 +21425,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>1553</v>
       </c>
@@ -19302,6 +21450,9 @@
       <c r="H389" t="s">
         <v>1556</v>
       </c>
+      <c r="I389" t="s">
+        <v>2219</v>
+      </c>
       <c r="J389" t="s">
         <v>15</v>
       </c>
@@ -19309,7 +21460,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>1557</v>
       </c>
@@ -19334,6 +21485,9 @@
       <c r="H390" t="s">
         <v>1560</v>
       </c>
+      <c r="I390" t="s">
+        <v>2220</v>
+      </c>
       <c r="J390" t="s">
         <v>15</v>
       </c>
@@ -19341,7 +21495,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>1561</v>
       </c>
@@ -19366,6 +21520,9 @@
       <c r="H391" t="s">
         <v>639</v>
       </c>
+      <c r="I391" t="s">
+        <v>2221</v>
+      </c>
       <c r="J391" t="s">
         <v>15</v>
       </c>
@@ -19373,7 +21530,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>1564</v>
       </c>
@@ -19398,6 +21555,9 @@
       <c r="H392" t="s">
         <v>403</v>
       </c>
+      <c r="I392" t="s">
+        <v>2222</v>
+      </c>
       <c r="J392" t="s">
         <v>15</v>
       </c>
@@ -19405,7 +21565,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>1568</v>
       </c>
@@ -19430,6 +21590,9 @@
       <c r="H393" t="s">
         <v>1302</v>
       </c>
+      <c r="I393" t="s">
+        <v>2223</v>
+      </c>
       <c r="J393" t="s">
         <v>15</v>
       </c>
@@ -19437,7 +21600,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>1572</v>
       </c>
@@ -19462,6 +21625,9 @@
       <c r="H394" t="s">
         <v>1575</v>
       </c>
+      <c r="I394" t="s">
+        <v>2224</v>
+      </c>
       <c r="J394" t="s">
         <v>15</v>
       </c>
@@ -19469,7 +21635,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>1576</v>
       </c>
@@ -19494,6 +21660,9 @@
       <c r="H395" t="s">
         <v>466</v>
       </c>
+      <c r="I395" t="s">
+        <v>2225</v>
+      </c>
       <c r="J395" t="s">
         <v>15</v>
       </c>
@@ -19501,7 +21670,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>1579</v>
       </c>
@@ -19526,6 +21695,9 @@
       <c r="H396" t="s">
         <v>1582</v>
       </c>
+      <c r="I396" t="s">
+        <v>2226</v>
+      </c>
       <c r="J396" t="s">
         <v>15</v>
       </c>
@@ -19533,7 +21705,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>1583</v>
       </c>
@@ -19558,6 +21730,9 @@
       <c r="H397" t="s">
         <v>1586</v>
       </c>
+      <c r="I397" t="s">
+        <v>2227</v>
+      </c>
       <c r="J397" t="s">
         <v>15</v>
       </c>
@@ -19565,7 +21740,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>1587</v>
       </c>
@@ -19590,6 +21765,9 @@
       <c r="H398" t="s">
         <v>782</v>
       </c>
+      <c r="I398" t="s">
+        <v>2228</v>
+      </c>
       <c r="J398" t="s">
         <v>15</v>
       </c>
@@ -19597,7 +21775,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>1591</v>
       </c>
@@ -19622,6 +21800,9 @@
       <c r="H399" t="s">
         <v>26</v>
       </c>
+      <c r="I399" t="s">
+        <v>2229</v>
+      </c>
       <c r="J399" t="s">
         <v>15</v>
       </c>
@@ -19629,7 +21810,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>1595</v>
       </c>
@@ -19654,6 +21835,9 @@
       <c r="H400" t="s">
         <v>790</v>
       </c>
+      <c r="I400" t="s">
+        <v>2230</v>
+      </c>
       <c r="J400" t="s">
         <v>15</v>
       </c>
@@ -19661,7 +21845,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>1598</v>
       </c>
@@ -19686,6 +21870,9 @@
       <c r="H401" t="s">
         <v>1602</v>
       </c>
+      <c r="I401" t="s">
+        <v>2231</v>
+      </c>
       <c r="J401" t="s">
         <v>15</v>
       </c>
@@ -19693,7 +21880,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>1603</v>
       </c>
@@ -19718,6 +21905,9 @@
       <c r="H402" t="s">
         <v>1606</v>
       </c>
+      <c r="I402" t="s">
+        <v>2232</v>
+      </c>
       <c r="J402" t="s">
         <v>15</v>
       </c>
@@ -19725,7 +21915,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>1607</v>
       </c>
@@ -19750,6 +21940,9 @@
       <c r="H403" t="s">
         <v>216</v>
       </c>
+      <c r="I403" t="s">
+        <v>2233</v>
+      </c>
       <c r="J403" t="s">
         <v>15</v>
       </c>
@@ -19757,7 +21950,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>1610</v>
       </c>
@@ -19782,6 +21975,9 @@
       <c r="H404" t="s">
         <v>82</v>
       </c>
+      <c r="I404" t="s">
+        <v>2234</v>
+      </c>
       <c r="J404" t="s">
         <v>15</v>
       </c>
@@ -19789,7 +21985,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>1615</v>
       </c>
@@ -19814,6 +22010,9 @@
       <c r="H405" t="s">
         <v>298</v>
       </c>
+      <c r="I405" t="s">
+        <v>2235</v>
+      </c>
       <c r="J405" t="s">
         <v>15</v>
       </c>
@@ -19821,7 +22020,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>1619</v>
       </c>
@@ -19846,6 +22045,9 @@
       <c r="H406" t="s">
         <v>1622</v>
       </c>
+      <c r="I406" t="s">
+        <v>2236</v>
+      </c>
       <c r="J406" t="s">
         <v>15</v>
       </c>
@@ -19853,7 +22055,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>1623</v>
       </c>
@@ -19878,6 +22080,9 @@
       <c r="H407" t="s">
         <v>1626</v>
       </c>
+      <c r="I407" t="s">
+        <v>2237</v>
+      </c>
       <c r="J407" t="s">
         <v>15</v>
       </c>
@@ -19885,7 +22090,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>1627</v>
       </c>
@@ -19910,6 +22115,9 @@
       <c r="H408" t="s">
         <v>1175</v>
       </c>
+      <c r="I408" t="s">
+        <v>2238</v>
+      </c>
       <c r="J408" t="s">
         <v>15</v>
       </c>
@@ -19917,7 +22125,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>1630</v>
       </c>
@@ -19942,6 +22150,9 @@
       <c r="H409" t="s">
         <v>1633</v>
       </c>
+      <c r="I409" t="s">
+        <v>2239</v>
+      </c>
       <c r="J409" t="s">
         <v>15</v>
       </c>
@@ -19949,7 +22160,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>1634</v>
       </c>
@@ -19974,6 +22185,9 @@
       <c r="H410" t="s">
         <v>180</v>
       </c>
+      <c r="I410" t="s">
+        <v>2240</v>
+      </c>
       <c r="J410" t="s">
         <v>15</v>
       </c>
@@ -19981,7 +22195,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>1637</v>
       </c>
@@ -20006,6 +22220,9 @@
       <c r="H411" t="s">
         <v>1640</v>
       </c>
+      <c r="I411" t="s">
+        <v>2436</v>
+      </c>
       <c r="J411" t="s">
         <v>15</v>
       </c>
@@ -20013,7 +22230,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>1641</v>
       </c>
@@ -20038,6 +22255,9 @@
       <c r="H412" t="s">
         <v>1644</v>
       </c>
+      <c r="I412" t="s">
+        <v>2241</v>
+      </c>
       <c r="J412" t="s">
         <v>15</v>
       </c>
@@ -20045,7 +22265,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>1645</v>
       </c>
@@ -20070,6 +22290,9 @@
       <c r="H413" t="s">
         <v>852</v>
       </c>
+      <c r="I413" t="s">
+        <v>2242</v>
+      </c>
       <c r="J413" t="s">
         <v>15</v>
       </c>
@@ -20077,7 +22300,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>1648</v>
       </c>
@@ -20102,6 +22325,9 @@
       <c r="H414" t="s">
         <v>73</v>
       </c>
+      <c r="I414" t="s">
+        <v>2243</v>
+      </c>
       <c r="J414" t="s">
         <v>15</v>
       </c>
@@ -20109,7 +22335,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>1650</v>
       </c>
@@ -20134,6 +22360,9 @@
       <c r="H415" t="s">
         <v>1654</v>
       </c>
+      <c r="I415" t="s">
+        <v>2244</v>
+      </c>
       <c r="J415" t="s">
         <v>15</v>
       </c>
@@ -20141,7 +22370,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>1655</v>
       </c>
@@ -20166,6 +22395,9 @@
       <c r="H416" t="s">
         <v>1658</v>
       </c>
+      <c r="I416" t="s">
+        <v>2245</v>
+      </c>
       <c r="J416" t="s">
         <v>15</v>
       </c>
@@ -20173,7 +22405,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>1659</v>
       </c>
@@ -20198,6 +22430,9 @@
       <c r="H417" t="s">
         <v>1662</v>
       </c>
+      <c r="I417" t="s">
+        <v>2246</v>
+      </c>
       <c r="J417" t="s">
         <v>15</v>
       </c>
@@ -20205,7 +22440,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>1663</v>
       </c>
@@ -20230,6 +22465,9 @@
       <c r="H418" t="s">
         <v>1667</v>
       </c>
+      <c r="I418" t="s">
+        <v>2247</v>
+      </c>
       <c r="J418" t="s">
         <v>15</v>
       </c>
@@ -20237,7 +22475,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>1668</v>
       </c>
@@ -20262,6 +22500,9 @@
       <c r="H419" t="s">
         <v>1582</v>
       </c>
+      <c r="I419" s="2" t="s">
+        <v>2248</v>
+      </c>
       <c r="J419" t="s">
         <v>15</v>
       </c>
@@ -20269,7 +22510,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>1671</v>
       </c>
@@ -20294,6 +22535,9 @@
       <c r="H420" t="s">
         <v>1546</v>
       </c>
+      <c r="I420" t="s">
+        <v>2249</v>
+      </c>
       <c r="J420" t="s">
         <v>15</v>
       </c>
@@ -20301,7 +22545,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>1675</v>
       </c>
@@ -20326,6 +22570,9 @@
       <c r="H421" t="s">
         <v>1452</v>
       </c>
+      <c r="I421" t="s">
+        <v>2250</v>
+      </c>
       <c r="J421" t="s">
         <v>15</v>
       </c>
@@ -20333,7 +22580,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>1678</v>
       </c>
@@ -20358,6 +22605,9 @@
       <c r="H422" t="s">
         <v>1681</v>
       </c>
+      <c r="I422" t="s">
+        <v>2251</v>
+      </c>
       <c r="J422" t="s">
         <v>15</v>
       </c>
@@ -20365,7 +22615,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>1682</v>
       </c>
@@ -20390,6 +22640,9 @@
       <c r="H423" t="s">
         <v>303</v>
       </c>
+      <c r="I423" t="s">
+        <v>2252</v>
+      </c>
       <c r="J423" t="s">
         <v>15</v>
       </c>
@@ -20397,7 +22650,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>1685</v>
       </c>
@@ -20422,6 +22675,9 @@
       <c r="H424" t="s">
         <v>1689</v>
       </c>
+      <c r="I424" t="s">
+        <v>2253</v>
+      </c>
       <c r="J424" t="s">
         <v>15</v>
       </c>
@@ -20429,7 +22685,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>1690</v>
       </c>
@@ -20454,6 +22710,9 @@
       <c r="H425" t="s">
         <v>1693</v>
       </c>
+      <c r="I425" t="s">
+        <v>2254</v>
+      </c>
       <c r="J425" t="s">
         <v>15</v>
       </c>
@@ -20461,7 +22720,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>1694</v>
       </c>
@@ -20486,6 +22745,9 @@
       <c r="H426" t="s">
         <v>1644</v>
       </c>
+      <c r="I426" t="s">
+        <v>2255</v>
+      </c>
       <c r="J426" t="s">
         <v>15</v>
       </c>
@@ -20493,7 +22755,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>1698</v>
       </c>
@@ -20518,6 +22780,9 @@
       <c r="H427" t="s">
         <v>1701</v>
       </c>
+      <c r="I427" t="s">
+        <v>2256</v>
+      </c>
       <c r="J427" t="s">
         <v>15</v>
       </c>
@@ -20525,7 +22790,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>1702</v>
       </c>
@@ -20550,6 +22815,9 @@
       <c r="H428" t="s">
         <v>1705</v>
       </c>
+      <c r="I428" t="s">
+        <v>2257</v>
+      </c>
       <c r="J428" t="s">
         <v>15</v>
       </c>
@@ -20557,7 +22825,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>1706</v>
       </c>
@@ -20582,6 +22850,9 @@
       <c r="H429" t="s">
         <v>31</v>
       </c>
+      <c r="I429" t="s">
+        <v>2258</v>
+      </c>
       <c r="J429" t="s">
         <v>15</v>
       </c>
@@ -20589,7 +22860,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>1709</v>
       </c>
@@ -20614,6 +22885,9 @@
       <c r="H430" t="s">
         <v>939</v>
       </c>
+      <c r="I430" t="s">
+        <v>2259</v>
+      </c>
       <c r="J430" t="s">
         <v>15</v>
       </c>
@@ -20621,7 +22895,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>1712</v>
       </c>
@@ -20646,6 +22920,9 @@
       <c r="H431" t="s">
         <v>324</v>
       </c>
+      <c r="I431" t="s">
+        <v>2260</v>
+      </c>
       <c r="J431" t="s">
         <v>15</v>
       </c>
@@ -20653,7 +22930,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>1715</v>
       </c>
@@ -20678,6 +22955,9 @@
       <c r="H432" t="s">
         <v>1718</v>
       </c>
+      <c r="I432" t="s">
+        <v>2261</v>
+      </c>
       <c r="J432" t="s">
         <v>15</v>
       </c>
@@ -20685,7 +22965,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>1719</v>
       </c>
@@ -20710,6 +22990,9 @@
       <c r="H433" t="s">
         <v>839</v>
       </c>
+      <c r="I433" t="s">
+        <v>2262</v>
+      </c>
       <c r="J433" t="s">
         <v>15</v>
       </c>
@@ -20717,7 +23000,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>1723</v>
       </c>
@@ -20742,6 +23025,9 @@
       <c r="H434" t="s">
         <v>758</v>
       </c>
+      <c r="I434" t="s">
+        <v>2263</v>
+      </c>
       <c r="J434" t="s">
         <v>15</v>
       </c>
@@ -20749,7 +23035,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>1726</v>
       </c>
@@ -20774,6 +23060,9 @@
       <c r="H435" t="s">
         <v>1058</v>
       </c>
+      <c r="I435" t="s">
+        <v>2264</v>
+      </c>
       <c r="J435" t="s">
         <v>15</v>
       </c>
@@ -20781,7 +23070,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>1729</v>
       </c>
@@ -20806,6 +23095,9 @@
       <c r="H436" t="s">
         <v>1733</v>
       </c>
+      <c r="I436" t="s">
+        <v>2427</v>
+      </c>
       <c r="J436" t="s">
         <v>15</v>
       </c>
@@ -20813,7 +23105,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>1734</v>
       </c>
@@ -20838,6 +23130,9 @@
       <c r="H437" t="s">
         <v>1737</v>
       </c>
+      <c r="I437" t="s">
+        <v>2265</v>
+      </c>
       <c r="J437" t="s">
         <v>15</v>
       </c>
@@ -20845,7 +23140,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>1738</v>
       </c>
@@ -20870,6 +23165,9 @@
       <c r="H438" t="s">
         <v>1742</v>
       </c>
+      <c r="I438" t="s">
+        <v>2266</v>
+      </c>
       <c r="J438" t="s">
         <v>15</v>
       </c>
@@ -20877,7 +23175,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>1743</v>
       </c>
@@ -20902,6 +23200,9 @@
       <c r="H439" t="s">
         <v>977</v>
       </c>
+      <c r="I439" t="s">
+        <v>2267</v>
+      </c>
       <c r="J439" t="s">
         <v>15</v>
       </c>
@@ -20909,7 +23210,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>1747</v>
       </c>
@@ -20934,6 +23235,9 @@
       <c r="H440" t="s">
         <v>1443</v>
       </c>
+      <c r="I440" t="s">
+        <v>2268</v>
+      </c>
       <c r="J440" t="s">
         <v>15</v>
       </c>
@@ -20941,7 +23245,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>1750</v>
       </c>
@@ -20966,6 +23270,9 @@
       <c r="H441" t="s">
         <v>1302</v>
       </c>
+      <c r="I441" t="s">
+        <v>2269</v>
+      </c>
       <c r="J441" t="s">
         <v>15</v>
       </c>
@@ -20973,7 +23280,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>1753</v>
       </c>
@@ -20998,6 +23305,9 @@
       <c r="H442" t="s">
         <v>1756</v>
       </c>
+      <c r="I442" t="s">
+        <v>2270</v>
+      </c>
       <c r="J442" t="s">
         <v>15</v>
       </c>
@@ -21005,7 +23315,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>1757</v>
       </c>
@@ -21030,6 +23340,9 @@
       <c r="H443" t="s">
         <v>36</v>
       </c>
+      <c r="I443" t="s">
+        <v>2271</v>
+      </c>
       <c r="J443" t="s">
         <v>15</v>
       </c>
@@ -21037,7 +23350,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>1760</v>
       </c>
@@ -21062,6 +23375,9 @@
       <c r="H444" t="s">
         <v>20</v>
       </c>
+      <c r="I444" t="s">
+        <v>2272</v>
+      </c>
       <c r="J444" t="s">
         <v>15</v>
       </c>
@@ -21069,7 +23385,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>1763</v>
       </c>
@@ -21094,6 +23410,9 @@
       <c r="H445" t="s">
         <v>951</v>
       </c>
+      <c r="I445" t="s">
+        <v>2273</v>
+      </c>
       <c r="J445" t="s">
         <v>15</v>
       </c>
@@ -21101,7 +23420,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>1766</v>
       </c>
@@ -21126,7 +23445,9 @@
       <c r="H446" t="s">
         <v>1769</v>
       </c>
-      <c r="I446" s="2"/>
+      <c r="I446" t="s">
+        <v>2274</v>
+      </c>
       <c r="J446" t="s">
         <v>15</v>
       </c>
@@ -21134,7 +23455,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>1770</v>
       </c>
@@ -21159,6 +23480,9 @@
       <c r="H447" t="s">
         <v>229</v>
       </c>
+      <c r="I447" t="s">
+        <v>2275</v>
+      </c>
       <c r="J447" t="s">
         <v>15</v>
       </c>
@@ -21166,7 +23490,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>1773</v>
       </c>
@@ -21191,6 +23515,9 @@
       <c r="H448" t="s">
         <v>1046</v>
       </c>
+      <c r="I448" t="s">
+        <v>2276</v>
+      </c>
       <c r="J448" t="s">
         <v>15</v>
       </c>
@@ -21198,7 +23525,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>1776</v>
       </c>
@@ -21223,6 +23550,9 @@
       <c r="H449" t="s">
         <v>852</v>
       </c>
+      <c r="I449" t="s">
+        <v>2277</v>
+      </c>
       <c r="J449" t="s">
         <v>15</v>
       </c>
@@ -21230,7 +23560,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>1779</v>
       </c>
@@ -21255,6 +23585,9 @@
       <c r="H450" t="s">
         <v>1783</v>
       </c>
+      <c r="I450" t="s">
+        <v>2278</v>
+      </c>
       <c r="J450" t="s">
         <v>15</v>
       </c>
@@ -21262,7 +23595,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>1784</v>
       </c>
@@ -21287,6 +23620,9 @@
       <c r="H451" t="s">
         <v>524</v>
       </c>
+      <c r="I451" t="s">
+        <v>2279</v>
+      </c>
       <c r="J451" t="s">
         <v>15</v>
       </c>
@@ -21294,7 +23630,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>1788</v>
       </c>
@@ -21319,6 +23655,9 @@
       <c r="H452" t="s">
         <v>717</v>
       </c>
+      <c r="I452" t="s">
+        <v>2280</v>
+      </c>
       <c r="J452" t="s">
         <v>15</v>
       </c>
@@ -21326,7 +23665,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>1791</v>
       </c>
@@ -21351,6 +23690,9 @@
       <c r="H453" t="s">
         <v>73</v>
       </c>
+      <c r="I453" t="s">
+        <v>2281</v>
+      </c>
       <c r="J453" t="s">
         <v>15</v>
       </c>
@@ -21358,7 +23700,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>1794</v>
       </c>
@@ -21383,6 +23725,9 @@
       <c r="H454" t="s">
         <v>1718</v>
       </c>
+      <c r="I454" t="s">
+        <v>2282</v>
+      </c>
       <c r="J454" t="s">
         <v>15</v>
       </c>
@@ -21390,7 +23735,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>1797</v>
       </c>
@@ -21415,6 +23760,9 @@
       <c r="H455" t="s">
         <v>934</v>
       </c>
+      <c r="I455" t="s">
+        <v>2283</v>
+      </c>
       <c r="J455" t="s">
         <v>15</v>
       </c>
@@ -21422,7 +23770,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>1800</v>
       </c>
@@ -21447,6 +23795,9 @@
       <c r="H456" t="s">
         <v>92</v>
       </c>
+      <c r="I456" t="s">
+        <v>2284</v>
+      </c>
       <c r="J456" t="s">
         <v>15</v>
       </c>
@@ -21454,7 +23805,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>1803</v>
       </c>
@@ -21479,6 +23830,9 @@
       <c r="H457" t="s">
         <v>1806</v>
       </c>
+      <c r="I457" t="s">
+        <v>2285</v>
+      </c>
       <c r="J457" t="s">
         <v>15</v>
       </c>
@@ -21486,7 +23840,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>1807</v>
       </c>
@@ -21511,6 +23865,9 @@
       <c r="H458" t="s">
         <v>115</v>
       </c>
+      <c r="I458" t="s">
+        <v>2286</v>
+      </c>
       <c r="J458" t="s">
         <v>15</v>
       </c>
@@ -21518,7 +23875,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>1811</v>
       </c>
@@ -21543,6 +23900,9 @@
       <c r="H459" t="s">
         <v>294</v>
       </c>
+      <c r="I459" t="s">
+        <v>2287</v>
+      </c>
       <c r="J459" t="s">
         <v>15</v>
       </c>
@@ -21550,7 +23910,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>1814</v>
       </c>
@@ -21575,6 +23935,9 @@
       <c r="H460" t="s">
         <v>1817</v>
       </c>
+      <c r="I460" t="s">
+        <v>2288</v>
+      </c>
       <c r="J460" t="s">
         <v>15</v>
       </c>
@@ -21582,7 +23945,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>1818</v>
       </c>
@@ -21607,6 +23970,9 @@
       <c r="H461" t="s">
         <v>620</v>
       </c>
+      <c r="I461" t="s">
+        <v>2289</v>
+      </c>
       <c r="J461" t="s">
         <v>15</v>
       </c>
@@ -21614,7 +23980,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>1821</v>
       </c>
@@ -21639,6 +24005,9 @@
       <c r="H462" t="s">
         <v>1667</v>
       </c>
+      <c r="I462" t="s">
+        <v>2290</v>
+      </c>
       <c r="J462" t="s">
         <v>15</v>
       </c>
@@ -21646,7 +24015,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>1824</v>
       </c>
@@ -21671,6 +24040,9 @@
       <c r="H463" t="s">
         <v>1827</v>
       </c>
+      <c r="I463" t="s">
+        <v>2291</v>
+      </c>
       <c r="J463" t="s">
         <v>15</v>
       </c>
@@ -21678,7 +24050,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>1828</v>
       </c>
@@ -21703,6 +24075,9 @@
       <c r="H464" t="s">
         <v>639</v>
       </c>
+      <c r="I464" t="s">
+        <v>2292</v>
+      </c>
       <c r="J464" t="s">
         <v>15</v>
       </c>
@@ -21710,7 +24085,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>1831</v>
       </c>
@@ -21735,6 +24110,9 @@
       <c r="H465" t="s">
         <v>461</v>
       </c>
+      <c r="I465" t="s">
+        <v>2293</v>
+      </c>
       <c r="J465" t="s">
         <v>15</v>
       </c>
@@ -21742,7 +24120,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>1835</v>
       </c>
@@ -21767,6 +24145,9 @@
       <c r="H466" t="s">
         <v>1438</v>
       </c>
+      <c r="I466" t="s">
+        <v>2294</v>
+      </c>
       <c r="J466" t="s">
         <v>15</v>
       </c>
@@ -21774,7 +24155,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>1838</v>
       </c>
@@ -21799,6 +24180,9 @@
       <c r="H467" t="s">
         <v>1841</v>
       </c>
+      <c r="I467" t="s">
+        <v>2295</v>
+      </c>
       <c r="J467" t="s">
         <v>15</v>
       </c>
@@ -21806,7 +24190,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>1842</v>
       </c>
@@ -21831,6 +24215,9 @@
       <c r="H468" t="s">
         <v>1846</v>
       </c>
+      <c r="I468" t="s">
+        <v>2296</v>
+      </c>
       <c r="J468" t="s">
         <v>15</v>
       </c>
@@ -21838,7 +24225,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>1847</v>
       </c>
@@ -21863,6 +24250,9 @@
       <c r="H469" t="s">
         <v>1850</v>
       </c>
+      <c r="I469" t="s">
+        <v>2297</v>
+      </c>
       <c r="J469" t="s">
         <v>15</v>
       </c>
@@ -21870,7 +24260,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>1851</v>
       </c>
@@ -21895,6 +24285,9 @@
       <c r="H470" t="s">
         <v>20</v>
       </c>
+      <c r="I470" t="s">
+        <v>2298</v>
+      </c>
       <c r="J470" t="s">
         <v>15</v>
       </c>
@@ -21902,7 +24295,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>1854</v>
       </c>
@@ -21927,6 +24320,9 @@
       <c r="H471" t="s">
         <v>1857</v>
       </c>
+      <c r="I471" t="s">
+        <v>2299</v>
+      </c>
       <c r="J471" t="s">
         <v>15</v>
       </c>
@@ -21934,7 +24330,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>1858</v>
       </c>
@@ -21959,6 +24355,9 @@
       <c r="H472" t="s">
         <v>895</v>
       </c>
+      <c r="I472" t="s">
+        <v>2300</v>
+      </c>
       <c r="J472" t="s">
         <v>15</v>
       </c>
@@ -21966,7 +24365,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>1862</v>
       </c>
@@ -21991,6 +24390,9 @@
       <c r="H473" t="s">
         <v>1865</v>
       </c>
+      <c r="I473" t="s">
+        <v>2301</v>
+      </c>
       <c r="J473" t="s">
         <v>15</v>
       </c>
@@ -21998,7 +24400,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>1866</v>
       </c>
@@ -22023,6 +24425,9 @@
       <c r="H474" t="s">
         <v>1869</v>
       </c>
+      <c r="I474" t="s">
+        <v>2302</v>
+      </c>
       <c r="J474" t="s">
         <v>15</v>
       </c>
@@ -22030,7 +24435,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>1870</v>
       </c>
@@ -22055,6 +24460,9 @@
       <c r="H475" t="s">
         <v>411</v>
       </c>
+      <c r="I475" t="s">
+        <v>2303</v>
+      </c>
       <c r="J475" t="s">
         <v>15</v>
       </c>
@@ -22062,7 +24470,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>1873</v>
       </c>
@@ -22087,6 +24495,9 @@
       <c r="H476" t="s">
         <v>1876</v>
       </c>
+      <c r="I476" t="s">
+        <v>2304</v>
+      </c>
       <c r="J476" t="s">
         <v>1877</v>
       </c>
@@ -22094,7 +24505,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>1878</v>
       </c>
@@ -22119,6 +24530,9 @@
       <c r="H477" t="s">
         <v>1882</v>
       </c>
+      <c r="I477" t="s">
+        <v>2305</v>
+      </c>
       <c r="J477" t="s">
         <v>15</v>
       </c>
@@ -22126,7 +24540,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>1883</v>
       </c>
@@ -22151,6 +24565,9 @@
       <c r="H478" t="s">
         <v>1226</v>
       </c>
+      <c r="I478" t="s">
+        <v>2428</v>
+      </c>
       <c r="J478" t="s">
         <v>15</v>
       </c>
@@ -22158,7 +24575,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>1886</v>
       </c>
@@ -22183,6 +24600,9 @@
       <c r="H479" t="s">
         <v>243</v>
       </c>
+      <c r="I479" t="s">
+        <v>2306</v>
+      </c>
       <c r="J479" t="s">
         <v>15</v>
       </c>
@@ -22190,7 +24610,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>1889</v>
       </c>
@@ -22215,6 +24635,9 @@
       <c r="H480" t="s">
         <v>1893</v>
       </c>
+      <c r="I480" t="s">
+        <v>2307</v>
+      </c>
       <c r="J480" t="s">
         <v>15</v>
       </c>
@@ -22222,7 +24645,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>1894</v>
       </c>
@@ -22247,6 +24670,9 @@
       <c r="H481" t="s">
         <v>934</v>
       </c>
+      <c r="I481" t="s">
+        <v>2308</v>
+      </c>
       <c r="J481" t="s">
         <v>15</v>
       </c>
@@ -22254,7 +24680,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>1898</v>
       </c>
@@ -22279,6 +24705,9 @@
       <c r="H482" t="s">
         <v>1901</v>
       </c>
+      <c r="I482" t="s">
+        <v>2429</v>
+      </c>
       <c r="J482" t="s">
         <v>15</v>
       </c>
@@ -22286,7 +24715,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>1902</v>
       </c>
@@ -22311,6 +24740,9 @@
       <c r="H483" t="s">
         <v>1906</v>
       </c>
+      <c r="I483" t="s">
+        <v>2309</v>
+      </c>
       <c r="J483" t="s">
         <v>15</v>
       </c>
@@ -22318,7 +24750,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>1907</v>
       </c>
@@ -22343,6 +24775,9 @@
       <c r="H484" t="s">
         <v>332</v>
       </c>
+      <c r="I484" t="s">
+        <v>2310</v>
+      </c>
       <c r="J484" t="s">
         <v>15</v>
       </c>
@@ -22350,7 +24785,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>1910</v>
       </c>
@@ -22375,6 +24810,9 @@
       <c r="H485" t="s">
         <v>1452</v>
       </c>
+      <c r="I485" t="s">
+        <v>2311</v>
+      </c>
       <c r="J485" t="s">
         <v>15</v>
       </c>
@@ -22382,7 +24820,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>1913</v>
       </c>
@@ -22407,6 +24845,9 @@
       <c r="H486" t="s">
         <v>1701</v>
       </c>
+      <c r="I486" t="s">
+        <v>2312</v>
+      </c>
       <c r="J486" t="s">
         <v>15</v>
       </c>
@@ -22414,7 +24855,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>1916</v>
       </c>
@@ -22439,6 +24880,9 @@
       <c r="H487" t="s">
         <v>1919</v>
       </c>
+      <c r="I487" t="s">
+        <v>2313</v>
+      </c>
       <c r="J487" t="s">
         <v>15</v>
       </c>
@@ -22446,7 +24890,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>1920</v>
       </c>
@@ -22471,6 +24915,9 @@
       <c r="H488" t="s">
         <v>172</v>
       </c>
+      <c r="I488" t="s">
+        <v>2314</v>
+      </c>
       <c r="J488" t="s">
         <v>15</v>
       </c>
@@ -22478,7 +24925,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>1924</v>
       </c>
@@ -22503,6 +24950,9 @@
       <c r="H489" t="s">
         <v>1927</v>
       </c>
+      <c r="I489" t="s">
+        <v>2315</v>
+      </c>
       <c r="J489" t="s">
         <v>15</v>
       </c>
@@ -22510,7 +24960,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>1928</v>
       </c>
@@ -22535,6 +24985,9 @@
       <c r="H490" t="s">
         <v>1931</v>
       </c>
+      <c r="I490" t="s">
+        <v>2316</v>
+      </c>
       <c r="J490" t="s">
         <v>15</v>
       </c>
@@ -22542,7 +24995,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>1932</v>
       </c>
@@ -22567,6 +25020,9 @@
       <c r="H491" t="s">
         <v>31</v>
       </c>
+      <c r="I491" t="s">
+        <v>2430</v>
+      </c>
       <c r="J491" t="s">
         <v>1944</v>
       </c>
@@ -22574,7 +25030,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>1935</v>
       </c>
@@ -22599,6 +25055,9 @@
       <c r="H492" t="s">
         <v>1938</v>
       </c>
+      <c r="I492" t="s">
+        <v>2317</v>
+      </c>
       <c r="J492" t="s">
         <v>15</v>
       </c>
@@ -22606,7 +25065,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>1939</v>
       </c>
@@ -22631,6 +25090,9 @@
       <c r="H493" t="s">
         <v>1942</v>
       </c>
+      <c r="I493" t="s">
+        <v>2318</v>
+      </c>
       <c r="J493" t="s">
         <v>15</v>
       </c>
@@ -22640,6 +25102,109 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I216" r:id="rId1" xr:uid="{8FBF1262-BD49-4A44-A947-7F8B12D7538B}"/>
+    <hyperlink ref="I201" r:id="rId2" xr:uid="{EFD7F607-9707-4537-A316-DCB2C11018F2}"/>
+    <hyperlink ref="I202" r:id="rId3" xr:uid="{EF5D5A1F-D873-4381-AC1D-653F94EA9ECC}"/>
+    <hyperlink ref="I203" r:id="rId4" xr:uid="{FB0E8790-4BC0-4F82-9A85-8FB0636FCD28}"/>
+    <hyperlink ref="I204" r:id="rId5" xr:uid="{9FB009DC-C8C0-46DB-BE57-9B2F0B8D908A}"/>
+    <hyperlink ref="I205" r:id="rId6" xr:uid="{53E0EEC0-5FBF-4BC8-AD51-DA1C3FA010DF}"/>
+    <hyperlink ref="I206" r:id="rId7" xr:uid="{2B2CCE25-B29F-4DE0-A291-86F44162FE36}"/>
+    <hyperlink ref="I207" r:id="rId8" xr:uid="{9A55F159-DCDE-470F-A45E-395B9B5AB70D}"/>
+    <hyperlink ref="I208" r:id="rId9" xr:uid="{E7614CE9-9558-4A6E-997A-C1D37C47547F}"/>
+    <hyperlink ref="I209" r:id="rId10" xr:uid="{20364688-D939-47F5-9739-AB126648BDE4}"/>
+    <hyperlink ref="I210" r:id="rId11" xr:uid="{F061F71C-0688-4F2C-99FD-A31020B50F99}"/>
+    <hyperlink ref="I211" r:id="rId12" xr:uid="{B97A9B2D-3FB4-4A46-93BE-90FAD0858E21}"/>
+    <hyperlink ref="I212" r:id="rId13" xr:uid="{4941B01C-2E46-491F-BD9A-96CE1FE4F244}"/>
+    <hyperlink ref="I213" r:id="rId14" xr:uid="{1A0CBB4D-CBA3-4644-B11D-59556C546AAB}"/>
+    <hyperlink ref="I214" r:id="rId15" xr:uid="{92C68F94-6461-407F-B3BF-D81486FB3AB1}"/>
+    <hyperlink ref="I215" r:id="rId16" xr:uid="{3EF78117-0DA4-4D4E-8D22-4C5572FFE72E}"/>
+    <hyperlink ref="I217" r:id="rId17" xr:uid="{5FE31920-9F73-4D8B-BF79-3C2C9C143D9C}"/>
+    <hyperlink ref="I219" r:id="rId18" xr:uid="{EF838D3C-E43F-4812-97E1-84F6DD8D6C3E}"/>
+    <hyperlink ref="I220" r:id="rId19" xr:uid="{B100D6CF-2683-4F72-ADDD-D58C82EF11AE}"/>
+    <hyperlink ref="I221" r:id="rId20" xr:uid="{D530AC15-84CC-4533-93FD-E1B9AE2A0BF2}"/>
+    <hyperlink ref="I222" r:id="rId21" xr:uid="{10D3821E-82A4-495E-80BC-58802189A82F}"/>
+    <hyperlink ref="I223" r:id="rId22" xr:uid="{DF92EE48-C54E-400A-923D-2977055CB438}"/>
+    <hyperlink ref="I225" r:id="rId23" xr:uid="{C9C2EF23-3D18-4311-8E97-7008053453C6}"/>
+    <hyperlink ref="I224" r:id="rId24" xr:uid="{F15AB712-B588-475E-A370-9E449FEDD421}"/>
+    <hyperlink ref="I226" r:id="rId25" xr:uid="{6A9C6A1C-BFCD-48F6-810A-E400B47DD830}"/>
+    <hyperlink ref="I227" r:id="rId26" xr:uid="{C296782E-B487-450E-BD81-A92E1032D48F}"/>
+    <hyperlink ref="I228" r:id="rId27" xr:uid="{7E563BB4-BB36-4917-ADD2-4611CCCDC20C}"/>
+    <hyperlink ref="I229" r:id="rId28" xr:uid="{116EF6DE-254C-4F12-BD45-3800783230BD}"/>
+    <hyperlink ref="I230" r:id="rId29" xr:uid="{3E19CE04-224A-4BD4-92BF-AEAB29FE7D52}"/>
+    <hyperlink ref="I231" r:id="rId30" xr:uid="{2AA1279F-1228-4B1E-8422-9B012216505F}"/>
+    <hyperlink ref="I232" r:id="rId31" xr:uid="{F8C2140A-F734-4664-B3F2-9BE98E73DDF0}"/>
+    <hyperlink ref="I233" r:id="rId32" xr:uid="{01FD31DF-2C13-49F5-AD6F-05BB2BBF3572}"/>
+    <hyperlink ref="I234" r:id="rId33" xr:uid="{6ED1E013-4DAE-4E0B-9D77-D46B9B74F602}"/>
+    <hyperlink ref="I235" r:id="rId34" xr:uid="{4DFD686A-08DC-46E5-8DD9-E052FC9516FB}"/>
+    <hyperlink ref="I238" r:id="rId35" xr:uid="{DB0B9BE5-7339-4761-808F-584060E4E7A7}"/>
+    <hyperlink ref="I236" r:id="rId36" xr:uid="{DF60D561-02C9-4C05-BC20-713292BF0FC4}"/>
+    <hyperlink ref="I237" r:id="rId37" xr:uid="{3EC942B9-C281-4E56-8609-B302412ABA5A}"/>
+    <hyperlink ref="I239" r:id="rId38" xr:uid="{A3922EA5-76DC-4D0C-A642-B25E702053DC}"/>
+    <hyperlink ref="I241" r:id="rId39" xr:uid="{34DCF899-0D47-496A-8AE9-C6C0FE916FF8}"/>
+    <hyperlink ref="I242" r:id="rId40" xr:uid="{8CBFC8D3-80D3-4441-A287-A6C7B9F43CB0}"/>
+    <hyperlink ref="I243" r:id="rId41" xr:uid="{4988B0A3-ED7F-48D4-AABD-C93487F44B20}"/>
+    <hyperlink ref="I244" r:id="rId42" xr:uid="{ECE9470A-E8AC-4FA8-AA48-814333A76BE5}"/>
+    <hyperlink ref="I245" r:id="rId43" xr:uid="{2DE3D082-6DF6-49B8-AAC0-86DF4D92456D}"/>
+    <hyperlink ref="I246" r:id="rId44" xr:uid="{D4258566-22DC-4262-B4CE-E3309A18110F}"/>
+    <hyperlink ref="I247" r:id="rId45" xr:uid="{E3B10453-F830-46A3-AFE9-DBCBE7C03C26}"/>
+    <hyperlink ref="I248" r:id="rId46" xr:uid="{3056E298-096E-42C3-90C0-AA17329FAE16}"/>
+    <hyperlink ref="I249" r:id="rId47" xr:uid="{D4359637-60A4-46C9-9D93-1B2609DD1B85}"/>
+    <hyperlink ref="I250" r:id="rId48" xr:uid="{C6E56E5D-7BA3-432A-A4AA-FF3C8B8DC520}"/>
+    <hyperlink ref="I251" r:id="rId49" xr:uid="{33814A20-692F-4D1E-9CA8-C7AB33070B30}"/>
+    <hyperlink ref="I253" r:id="rId50" xr:uid="{AB9B6C2E-8209-4618-849D-69C7EA01CE77}"/>
+    <hyperlink ref="I252" r:id="rId51" xr:uid="{5B09510B-7305-411B-93F5-FF8BF102B458}"/>
+    <hyperlink ref="I254" r:id="rId52" xr:uid="{D9998543-59D9-4F23-824F-8164057DAFAE}"/>
+    <hyperlink ref="I255" r:id="rId53" xr:uid="{5739A5C9-E4B0-4244-B59C-0B8CC1D3671B}"/>
+    <hyperlink ref="I256" r:id="rId54" xr:uid="{D2CB5995-E086-4A6A-A3CF-9480F9911D9C}"/>
+    <hyperlink ref="I257" r:id="rId55" xr:uid="{F809B2DE-67AF-4EA0-85C3-28750665E37D}"/>
+    <hyperlink ref="I258" r:id="rId56" xr:uid="{A626836D-291F-45CE-BC60-3E2F1E7A8ECB}"/>
+    <hyperlink ref="I259" r:id="rId57" xr:uid="{8A35A98C-A8CE-46F1-A0D0-501AB8EEF714}"/>
+    <hyperlink ref="I260" r:id="rId58" xr:uid="{1456D480-92B0-4BCC-A83F-96C8029B22D8}"/>
+    <hyperlink ref="I261" r:id="rId59" xr:uid="{0BD43CA9-399C-469B-B893-9F93064814C5}"/>
+    <hyperlink ref="I262" r:id="rId60" xr:uid="{B156D6F8-C221-47B9-9D24-FD1989EAAA8D}"/>
+    <hyperlink ref="I263" r:id="rId61" xr:uid="{AD601BBA-F72D-4D28-AFF7-B8DD83D32ED4}"/>
+    <hyperlink ref="I264" r:id="rId62" xr:uid="{51D2E652-6E6C-45BC-8B21-C010637815E7}"/>
+    <hyperlink ref="I265" r:id="rId63" xr:uid="{77BBCC89-9DDE-4E5D-90CB-84CE2785376F}"/>
+    <hyperlink ref="I266" r:id="rId64" xr:uid="{6209200F-0B4B-4886-9C69-631D807613D6}"/>
+    <hyperlink ref="I267" r:id="rId65" xr:uid="{80A34FD5-119E-49B1-A308-3EFE0B22AA59}"/>
+    <hyperlink ref="I268" r:id="rId66" xr:uid="{584383E7-BCE4-48B6-A0DB-53C2E0C63417}"/>
+    <hyperlink ref="I269" r:id="rId67" xr:uid="{6D317566-A00B-41D3-88F3-EBE3040ADBA9}"/>
+    <hyperlink ref="I270" r:id="rId68" xr:uid="{2AF94FAD-CAB0-4905-ABC6-83685FD414BE}"/>
+    <hyperlink ref="I271" r:id="rId69" xr:uid="{09DB996E-F4AF-4CFD-B6C2-A66ECAD57A7B}"/>
+    <hyperlink ref="I272" r:id="rId70" xr:uid="{6B502E7D-D748-46BD-8CF9-888DD3A5CE2B}"/>
+    <hyperlink ref="I273" r:id="rId71" xr:uid="{58F1DF7B-9E2B-4C63-968C-B3FB167ECF40}"/>
+    <hyperlink ref="I274" r:id="rId72" xr:uid="{212EF840-7363-4B18-A4F4-25A459904AC1}"/>
+    <hyperlink ref="I275" r:id="rId73" xr:uid="{471CB1D1-8FD0-4ECF-8600-75AE38D460A7}"/>
+    <hyperlink ref="I277" r:id="rId74" xr:uid="{138A95FB-CAF1-4960-AEFC-49D4E238453F}"/>
+    <hyperlink ref="I276" r:id="rId75" xr:uid="{D935F7A9-F429-41F2-BF98-A5D61A54682E}"/>
+    <hyperlink ref="I278" r:id="rId76" xr:uid="{E0CAAC37-487C-48C0-81DB-A1BBCB8D1150}"/>
+    <hyperlink ref="I279" r:id="rId77" xr:uid="{30E7B7C5-5EDB-4575-8796-FC92D09C239B}"/>
+    <hyperlink ref="I280" r:id="rId78" xr:uid="{40B99BAD-4ACB-4F54-B0FF-75C78C9C41A8}"/>
+    <hyperlink ref="I281" r:id="rId79" xr:uid="{CB8916D1-FB31-4C79-A7C6-E03AA857AFFC}"/>
+    <hyperlink ref="I282" r:id="rId80" xr:uid="{470BD278-A07B-47C9-8854-5B67FB1B6234}"/>
+    <hyperlink ref="I283" r:id="rId81" xr:uid="{DFCA8A19-58A5-4EA9-9CCE-6BFA21C0521F}"/>
+    <hyperlink ref="I284" r:id="rId82" xr:uid="{7E51FA2F-9ACF-4A68-B800-F7A8E2D2CAEE}"/>
+    <hyperlink ref="I285" r:id="rId83" xr:uid="{99045F7A-F771-408B-892C-0ACC197D8E4C}"/>
+    <hyperlink ref="I286" r:id="rId84" xr:uid="{6016FEA8-AEB9-42AD-BFFA-334358F288CD}"/>
+    <hyperlink ref="I288" r:id="rId85" xr:uid="{2C336E0A-131E-4557-A97F-48F97ADEBBA6}"/>
+    <hyperlink ref="I287" r:id="rId86" xr:uid="{3A00997E-90C3-4646-A0CB-2C16088E6B8D}"/>
+    <hyperlink ref="I289" r:id="rId87" xr:uid="{7A032BD7-C93A-40F9-BD67-42B35E597E42}"/>
+    <hyperlink ref="I290" r:id="rId88" xr:uid="{296812BA-9CE1-4988-B04D-0A0C3396DB3C}"/>
+    <hyperlink ref="I291" r:id="rId89" xr:uid="{13D98848-D9C4-4763-B950-CD52D9DEC4C1}"/>
+    <hyperlink ref="I292" r:id="rId90" xr:uid="{F03AE85C-C96E-4E5E-AF30-14909D788CC9}"/>
+    <hyperlink ref="I294" r:id="rId91" xr:uid="{C0059980-5E34-4F0A-95C1-F9BE8835D49C}"/>
+    <hyperlink ref="I293" r:id="rId92" xr:uid="{FCF984DF-D472-444B-BECF-8A3775401FEE}"/>
+    <hyperlink ref="I295" r:id="rId93" xr:uid="{2BB4193F-6DE7-4CE0-BA3B-140927FDD004}"/>
+    <hyperlink ref="I296" r:id="rId94" xr:uid="{00009B1C-8D31-4051-B546-D1F2E889C870}"/>
+    <hyperlink ref="I297" r:id="rId95" xr:uid="{A2BDA4BB-7D91-4C65-B9EF-AD60EE4A42FE}"/>
+    <hyperlink ref="I299" r:id="rId96" xr:uid="{DC036FCC-9549-4F7C-A229-7D5063340559}"/>
+    <hyperlink ref="I298" r:id="rId97" xr:uid="{88C18188-9922-449C-9E95-6E199B6E7D44}"/>
+    <hyperlink ref="I300" r:id="rId98" xr:uid="{29AF3242-6D31-4792-9E6A-E8BDD751AEBB}"/>
+    <hyperlink ref="I306" r:id="rId99" xr:uid="{A9AE1776-884E-4ECF-B2D0-2026246AD071}"/>
+    <hyperlink ref="I332" r:id="rId100" xr:uid="{3D1DF901-B102-4D84-A0CE-465EB2444D8D}"/>
+    <hyperlink ref="I419" r:id="rId101" xr:uid="{F3F0DAB9-8F95-4F45-80AC-CFF9C82EFC73}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>